--- a/data/問卷系統_月曆顯示.xlsx
+++ b/data/問卷系統_月曆顯示.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\271003\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e7512d0a0cfb7bd/公司電腦/^N研測課長業務/訓練排程上網/資料庫自動化雲端更新/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB8B947C-DC10-4575-8E62-9EB9280ACBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{BB8B947C-DC10-4575-8E62-9EB9280ACBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D9D8A33-D015-466F-B631-6985E1A6138B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,19 @@
     <sheet name="衝堂" sheetId="3" r:id="rId3"/>
     <sheet name="人員填寫狀況" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -375,9 +386,6 @@
     <t>5/26 三總</t>
   </si>
   <si>
-    <t>2026/3/20 大潭</t>
-  </si>
-  <si>
     <t>7/30 三總</t>
   </si>
   <si>
@@ -388,6 +396,10 @@
   </si>
   <si>
     <t>3/5 三總</t>
+  </si>
+  <si>
+    <t>2026/3/27 處內</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -761,7 +773,7 @@
   <dimension ref="A1:B47"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="13.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1251,7 +1263,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" ht="13.2">
       <c r="A2" s="4">
         <v>46078.482949444442</v>
       </c>
@@ -1274,7 +1286,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" ht="13.2">
       <c r="A3" s="4">
         <v>46078.484767696762</v>
       </c>
@@ -1297,7 +1309,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" ht="13.2">
       <c r="A4" s="4">
         <v>46078.484849120374</v>
       </c>
@@ -1323,7 +1335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" ht="13.2">
       <c r="A5" s="4">
         <v>46078.486714120372</v>
       </c>
@@ -1355,7 +1367,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" ht="13.2">
       <c r="A6" s="4">
         <v>46078.48830921296</v>
       </c>
@@ -1387,7 +1399,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" ht="13.2">
       <c r="A7" s="4">
         <v>46078.490101053241</v>
       </c>
@@ -1422,7 +1434,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" ht="13.2">
       <c r="A8" s="4">
         <v>46078.495963310183</v>
       </c>
@@ -1454,7 +1466,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" ht="13.2">
       <c r="A9" s="4">
         <v>46078.497951516205</v>
       </c>
@@ -1492,7 +1504,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" ht="13.2">
       <c r="A10" s="4">
         <v>46078.500472997686</v>
       </c>
@@ -1521,7 +1533,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" ht="13.2">
       <c r="A11" s="4">
         <v>46078.500563287038</v>
       </c>
@@ -1556,7 +1568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" ht="13.2">
       <c r="A12" s="4">
         <v>46078.520614456022</v>
       </c>
@@ -1588,7 +1600,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" ht="13.2">
       <c r="A13" s="4">
         <v>46078.564764513889</v>
       </c>
@@ -1620,7 +1632,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" ht="13.2">
       <c r="A14" s="4">
         <v>46078.568784780087</v>
       </c>
@@ -1643,7 +1655,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" ht="13.2">
       <c r="A15" s="4">
         <v>46078.568878067133</v>
       </c>
@@ -1678,7 +1690,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" ht="13.2">
       <c r="A16" s="4">
         <v>46078.574391724542</v>
       </c>
@@ -1710,7 +1722,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" ht="13.2">
       <c r="A17" s="4">
         <v>46078.578018553242</v>
       </c>
@@ -1733,7 +1745,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" ht="13.2">
       <c r="A18" s="4">
         <v>46078.617964687495</v>
       </c>
@@ -1750,7 +1762,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" ht="13.2">
       <c r="A19" s="4">
         <v>46078.651622349542</v>
       </c>
@@ -1776,7 +1788,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" ht="13.2">
       <c r="A20" s="4">
         <v>46078.667671388888</v>
       </c>
@@ -1811,7 +1823,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" ht="13.2">
       <c r="A21" s="4">
         <v>46079.435836782402</v>
       </c>
@@ -1828,7 +1840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" ht="13.2">
       <c r="A22" s="4">
         <v>46079.449516863431</v>
       </c>
@@ -1857,7 +1869,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" ht="13.2">
       <c r="A23" s="4">
         <v>46079.470154050927</v>
       </c>
@@ -1889,7 +1901,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" ht="13.2">
       <c r="A24" s="4">
         <v>46080.638196770829</v>
       </c>
@@ -1918,7 +1930,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" ht="13.2">
       <c r="A25" s="4">
         <v>46080.639740115745</v>
       </c>
@@ -1953,7 +1965,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" ht="13.2">
       <c r="A26" s="4">
         <v>46080.641628287034</v>
       </c>
@@ -1976,7 +1988,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" ht="13.2">
       <c r="A27" s="4">
         <v>46080.642606666668</v>
       </c>
@@ -2008,7 +2020,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" ht="13.2">
       <c r="A28" s="4">
         <v>46080.643336354166</v>
       </c>
@@ -2043,7 +2055,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" ht="13.2">
       <c r="A29" s="4">
         <v>46083.037841921294</v>
       </c>
@@ -2075,7 +2087,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" ht="13.2">
       <c r="A30" s="4">
         <v>46083.634491840276</v>
       </c>
@@ -2110,7 +2122,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" ht="13.2">
       <c r="A31" s="4">
         <v>46084.73660635417</v>
       </c>
@@ -2142,7 +2154,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" ht="13.2">
       <c r="A32" s="4">
         <v>46084.738894351853</v>
       </c>
@@ -2174,7 +2186,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:29">
+    <row r="33" spans="1:29" ht="13.2">
       <c r="A33" s="4">
         <v>46084.742841701387</v>
       </c>
@@ -2197,7 +2209,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:29">
+    <row r="34" spans="1:29" ht="13.2">
       <c r="A34" s="4">
         <v>46084.743685486115</v>
       </c>
@@ -2232,7 +2244,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
+    <row r="35" spans="1:29" ht="13.2">
       <c r="A35" s="4">
         <v>46084.76020355324</v>
       </c>
@@ -2261,7 +2273,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:29">
+    <row r="36" spans="1:29" ht="13.2">
       <c r="A36" s="4">
         <v>46084.801018819446</v>
       </c>
@@ -2284,7 +2296,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
+    <row r="37" spans="1:29" ht="13.2">
       <c r="A37" s="4">
         <v>46084.829352060187</v>
       </c>
@@ -2298,7 +2310,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:29">
+    <row r="38" spans="1:29" ht="13.2">
       <c r="A38" s="4">
         <v>46084.843648472219</v>
       </c>
@@ -2321,7 +2333,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:29">
+    <row r="39" spans="1:29" ht="13.2">
       <c r="A39" s="4">
         <v>46085.448310879627</v>
       </c>
@@ -2344,7 +2356,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:29">
+    <row r="40" spans="1:29" ht="13.2">
       <c r="A40" s="4">
         <v>46086.336962430556</v>
       </c>
@@ -2968,7 +2980,7 @@
       <c r="X57" s="15"/>
       <c r="Y57" s="15"/>
       <c r="Z57" s="14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AA57" s="15"/>
       <c r="AB57" s="12" t="s">
@@ -3080,7 +3092,7 @@
       </c>
       <c r="AA60" s="15"/>
       <c r="AB60" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AC60" s="15"/>
     </row>
@@ -3201,7 +3213,7 @@
       <c r="Q64" s="15"/>
       <c r="R64" s="15"/>
       <c r="S64" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T64" s="15"/>
       <c r="U64" s="15"/>
@@ -3246,7 +3258,7 @@
       </c>
       <c r="AA65" s="15"/>
       <c r="AB65" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC65" s="15"/>
     </row>
@@ -3282,7 +3294,7 @@
       </c>
       <c r="AA66" s="15"/>
       <c r="AB66" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC66" s="15"/>
     </row>

--- a/data/問卷系統_月曆顯示.xlsx
+++ b/data/問卷系統_月曆顯示.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e7512d0a0cfb7bd/公司電腦/^N研測課長業務/訓練排程上網/資料庫自動化雲端更新/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{BB8B947C-DC10-4575-8E62-9EB9280ACBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D9D8A33-D015-466F-B631-6985E1A6138B}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{BB8B947C-DC10-4575-8E62-9EB9280ACBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC741A96-6B13-49F9-B22A-BC857849B910}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="代碼設定" sheetId="1" r:id="rId1"/>
     <sheet name="回答紀錄" sheetId="2" r:id="rId2"/>
-    <sheet name="衝堂" sheetId="3" r:id="rId3"/>
-    <sheet name="人員填寫狀況" sheetId="4" r:id="rId4"/>
+    <sheet name="姓名代碼" sheetId="5" r:id="rId3"/>
+    <sheet name="衝堂" sheetId="3" r:id="rId4"/>
+    <sheet name="人員填寫狀況" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="164">
   <si>
     <t>代碼</t>
   </si>
@@ -400,17 +401,158 @@
   <si>
     <t>2026/3/27 處內</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡武哲</t>
+  </si>
+  <si>
+    <t>吳喬隆</t>
+  </si>
+  <si>
+    <t>李祐誠</t>
+  </si>
+  <si>
+    <t>陳嘉濬</t>
+  </si>
+  <si>
+    <t>吳忠憲</t>
+  </si>
+  <si>
+    <t>李翊菁</t>
+  </si>
+  <si>
+    <t>林玟均</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>林炳宏</t>
+  </si>
+  <si>
+    <t>陳柏均</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>李家緯</t>
+  </si>
+  <si>
+    <t>黃嵩捷</t>
+  </si>
+  <si>
+    <t>楊竣宇</t>
+  </si>
+  <si>
+    <t>呂侑儒</t>
+  </si>
+  <si>
+    <t>吳宇軒</t>
+  </si>
+  <si>
+    <t>李晨鍠</t>
+  </si>
+  <si>
+    <t>邱重豪</t>
+  </si>
+  <si>
+    <t>廖元瑜</t>
+  </si>
+  <si>
+    <t>蔡瀚承</t>
+  </si>
+  <si>
+    <t>陳  擎</t>
+  </si>
+  <si>
+    <t>吳祖年</t>
+  </si>
+  <si>
+    <t>陳思豪</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>林宏儒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>林士瑄</t>
+  </si>
+  <si>
+    <t>黃鴻鈞</t>
+  </si>
+  <si>
+    <t>鍾銘軒</t>
+  </si>
+  <si>
+    <t>李振誠</t>
+  </si>
+  <si>
+    <t>陳政瑋</t>
+  </si>
+  <si>
+    <t>徐振華</t>
+  </si>
+  <si>
+    <t>張謙凌</t>
+  </si>
+  <si>
+    <t>張志玄</t>
+  </si>
+  <si>
+    <t>李昇晉</t>
+  </si>
+  <si>
+    <t>張瑋岑</t>
+  </si>
+  <si>
+    <t>朱彥豪</t>
+  </si>
+  <si>
+    <t>陳廉淞</t>
+  </si>
+  <si>
+    <t>許庭彰</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>林時沂</t>
+  </si>
+  <si>
+    <t>張綺真</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳世龍</t>
+  </si>
+  <si>
+    <t>曾建銘</t>
+  </si>
+  <si>
+    <t>王冠博</t>
+  </si>
+  <si>
+    <t>楊智名</t>
+  </si>
+  <si>
+    <t>張承元</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>林郁軒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>王于任</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="177" formatCode="m/d"/>
+    <numFmt numFmtId="182" formatCode="0;\-0;;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -466,8 +608,46 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,8 +666,26 @@
         <bgColor rgb="FFF8F9FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -510,11 +708,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -547,6 +825,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3719,6 +4052,377 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA54FD3D-1D12-4247-9316-7162477C6C47}">
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.600000000000001" thickBot="1">
+      <c r="A1" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="18">
+        <v>121172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18">
+      <c r="A2" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="20">
+        <v>441802</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18">
+      <c r="A3" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="20">
+        <v>667903</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18">
+      <c r="A4" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="22">
+        <v>926941</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18">
+      <c r="A5" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="22">
+        <v>926814</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18">
+      <c r="A6" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="24">
+        <v>957504</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.600000000000001" thickBot="1">
+      <c r="A7" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="24">
+        <v>614230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18.600000000000001" thickBot="1">
+      <c r="A8" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="25">
+        <v>159297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18">
+      <c r="A9" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="20">
+        <v>365700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18">
+      <c r="A10" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="20">
+        <v>919946</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18">
+      <c r="A11" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="22">
+        <v>420099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18">
+      <c r="A12" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="22">
+        <v>424503</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18">
+      <c r="A13" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="27">
+        <v>798140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18">
+      <c r="A14" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="22">
+        <v>667790</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="18">
+      <c r="A15" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="27">
+        <v>813903</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18">
+      <c r="A16" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="22">
+        <v>926826</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18">
+      <c r="A17" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="22">
+        <v>926927</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18">
+      <c r="A18" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="27">
+        <v>958658</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="18">
+      <c r="A19" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="27">
+        <v>965552</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="18">
+      <c r="A20" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="27">
+        <v>969081</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18.600000000000001" thickBot="1">
+      <c r="A21" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="29">
+        <v>535474</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18.600000000000001" thickBot="1">
+      <c r="A22" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="25">
+        <v>271003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18">
+      <c r="A23" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="31">
+        <v>777829</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="18">
+      <c r="A24" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="20">
+        <v>438515</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18">
+      <c r="A25" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="22">
+        <v>420048</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18">
+      <c r="A26" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="22">
+        <v>572964</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="18">
+      <c r="A27" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="22">
+        <v>572990</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="18">
+      <c r="A28" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="22">
+        <v>667802</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="18">
+      <c r="A29" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="22">
+        <v>667725</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="18">
+      <c r="A30" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" s="27">
+        <v>813927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="18">
+      <c r="A31" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" s="27">
+        <v>926865</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="18">
+      <c r="A32" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="27">
+        <v>919959</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="18">
+      <c r="A33" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="27">
+        <v>956502</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="18">
+      <c r="A34" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="27">
+        <v>964698</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="18.600000000000001" thickBot="1">
+      <c r="A35" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B35" s="27">
+        <v>995225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="18.600000000000001" thickBot="1">
+      <c r="A36" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" s="25">
+        <v>613493</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="18">
+      <c r="A37" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B37" s="33">
+        <v>224307</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="18">
+      <c r="A38" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="33">
+        <v>440471</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="18">
+      <c r="A39" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="20">
+        <v>485918</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="18">
+      <c r="A40" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" s="35">
+        <v>660872</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="18">
+      <c r="A41" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" s="27">
+        <v>794418</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="18">
+      <c r="A42" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="B42" s="22">
+        <v>813675</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="18">
+      <c r="A43" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" s="22">
+        <v>900151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="18">
+      <c r="A44" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B44" s="22">
+        <v>977316</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="18">
+      <c r="A45" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="22">
+        <v>977328</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9758,7 +10462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/data/問卷系統_月曆顯示.xlsx
+++ b/data/問卷系統_月曆顯示.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECC08392-F0D9-4F5E-955A-2907E08D3B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CB8829-7084-4764-A52B-62C4DBF152E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -948,7 +948,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1051,11 +1051,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1139,6 +1150,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1154,10 +1168,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1751,7 +1761,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AB77"/>
+  <dimension ref="A1:AB78"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -3288,6 +3298,11 @@
     <row r="77" spans="2:28" ht="15.75" customHeight="1">
       <c r="B77" s="2">
         <v>535474</v>
+      </c>
+    </row>
+    <row r="78" spans="2:28" ht="15.75" customHeight="1">
+      <c r="B78" s="33">
+        <v>999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/問卷系統_月曆顯示.xlsx
+++ b/data/問卷系統_月曆顯示.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\271003\Desktop\Claude Office\工安自辦訓練表格填寫\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFC01C9-5E90-4A0C-816D-3EA08CC85C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84743BD2-D967-44A2-8F88-ABD319121CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="人員填寫情形" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">回答紀錄!$A$1:$AB$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">回答紀錄!$A$1:$AC$92</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="177">
   <si>
     <t>代碼</t>
   </si>
@@ -1558,12 +1558,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE92"/>
+  <dimension ref="A1:AB92"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" customWidth="1"/>
@@ -1573,18 +1572,17 @@
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="24.33203125" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" customWidth="1"/>
-    <col min="14" max="14" width="34.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" customHeight="1">
+    <row r="1" spans="1:28" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
+      <c r="C1" s="29" t="s">
+        <v>174</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>29</v>
@@ -1616,8 +1614,8 @@
       <c r="M1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>39</v>
+      <c r="N1" s="30" t="s">
+        <v>172</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>40</v>
@@ -1655,30 +1653,20 @@
       <c r="Z1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>52</v>
+      <c r="AA1" s="27" t="s">
+        <v>170</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AC1" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="AD1" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE1" s="29" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" ht="13.2">
+    </row>
+    <row r="2" spans="1:28" ht="13.2">
       <c r="A2" s="6">
         <v>46079.470154050927</v>
       </c>
       <c r="B2" s="7">
         <v>121172</v>
       </c>
-      <c r="C2" s="8"/>
       <c r="D2" s="9" t="s">
         <v>87</v>
       </c>
@@ -1705,7 +1693,6 @@
       <c r="M2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="8"/>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
@@ -1715,14 +1702,13 @@
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
     </row>
-    <row r="3" spans="1:31" ht="13.2">
+    <row r="3" spans="1:28" ht="13.2">
       <c r="A3" s="6">
         <v>46078.495963310183</v>
       </c>
       <c r="B3" s="7">
         <v>159297</v>
       </c>
-      <c r="C3" s="8"/>
       <c r="D3" s="9" t="s">
         <v>54</v>
       </c>
@@ -1749,7 +1735,6 @@
       <c r="M3" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
@@ -1759,14 +1744,13 @@
       <c r="U3" s="8"/>
       <c r="V3" s="8"/>
     </row>
-    <row r="4" spans="1:31" ht="13.2">
+    <row r="4" spans="1:28" ht="13.2">
       <c r="A4" s="6">
         <v>46078.667671388888</v>
       </c>
       <c r="B4" s="7">
         <v>271003</v>
       </c>
-      <c r="C4" s="8"/>
       <c r="D4" s="9" t="s">
         <v>54</v>
       </c>
@@ -1795,7 +1779,6 @@
       <c r="M4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
@@ -1805,14 +1788,13 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
     </row>
-    <row r="5" spans="1:31" ht="13.2">
+    <row r="5" spans="1:28" ht="13.2">
       <c r="A5" s="6">
         <v>46078.497951516205</v>
       </c>
       <c r="B5" s="7">
         <v>420048</v>
       </c>
-      <c r="C5" s="8"/>
       <c r="D5" s="9" t="s">
         <v>54</v>
       </c>
@@ -1841,7 +1823,6 @@
       <c r="M5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
@@ -1851,14 +1832,13 @@
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
     </row>
-    <row r="6" spans="1:31" ht="16.2">
+    <row r="6" spans="1:28" ht="16.2">
       <c r="A6" s="6">
         <v>46080.643336354166</v>
       </c>
       <c r="B6" s="7">
         <v>365700</v>
       </c>
-      <c r="C6" s="8"/>
       <c r="D6" s="9" t="s">
         <v>78</v>
       </c>
@@ -1887,7 +1867,6 @@
       <c r="M6" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
@@ -1906,14 +1885,13 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="13.2">
+    <row r="7" spans="1:28" ht="13.2">
       <c r="A7" s="6">
         <v>46078.564764513889</v>
       </c>
       <c r="B7" s="7">
         <v>420099</v>
       </c>
-      <c r="C7" s="8"/>
       <c r="D7" s="9" t="s">
         <v>78</v>
       </c>
@@ -1940,7 +1918,6 @@
       <c r="M7" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
@@ -1950,14 +1927,13 @@
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
-    <row r="8" spans="1:31" ht="16.2">
+    <row r="8" spans="1:28" ht="16.2">
       <c r="A8" s="6">
         <v>46083.037832708331</v>
       </c>
       <c r="B8" s="7">
         <v>424503</v>
       </c>
-      <c r="C8" s="8"/>
       <c r="D8" s="9" t="s">
         <v>54</v>
       </c>
@@ -1984,7 +1960,6 @@
       <c r="M8" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
@@ -2000,14 +1975,13 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="13.2">
+    <row r="9" spans="1:28" ht="13.2">
       <c r="A9" s="6">
         <v>46078.574391724542</v>
       </c>
       <c r="B9" s="7">
         <v>438515</v>
       </c>
-      <c r="C9" s="8"/>
       <c r="D9" s="9" t="s">
         <v>54</v>
       </c>
@@ -2034,7 +2008,6 @@
       </c>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
-      <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
@@ -2044,14 +2017,13 @@
       <c r="U9" s="8"/>
       <c r="V9" s="8"/>
     </row>
-    <row r="10" spans="1:31" ht="13.2">
+    <row r="10" spans="1:28" ht="13.2">
       <c r="A10" s="6">
         <v>46084.843648472219</v>
       </c>
       <c r="B10" s="7">
         <v>440471</v>
       </c>
-      <c r="C10" s="8"/>
       <c r="D10" s="9" t="s">
         <v>68</v>
       </c>
@@ -2072,7 +2044,6 @@
       <c r="K10" s="8"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
@@ -2082,14 +2053,13 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
     </row>
-    <row r="11" spans="1:31" ht="16.2">
+    <row r="11" spans="1:28" ht="16.2">
       <c r="A11" s="6">
         <v>46083.037841921294</v>
       </c>
       <c r="B11" s="7">
         <v>424503</v>
       </c>
-      <c r="C11" s="8"/>
       <c r="D11" s="9" t="s">
         <v>54</v>
       </c>
@@ -2116,7 +2086,6 @@
       <c r="M11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
@@ -2132,14 +2101,13 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="13.2">
+    <row r="12" spans="1:28" ht="13.2">
       <c r="A12" s="6">
         <v>46078.568878067133</v>
       </c>
       <c r="B12" s="7">
         <v>441802</v>
       </c>
-      <c r="C12" s="8"/>
       <c r="D12" s="9" t="s">
         <v>78</v>
       </c>
@@ -2168,7 +2136,6 @@
         <v>82</v>
       </c>
       <c r="M12" s="9"/>
-      <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
@@ -2179,14 +2146,13 @@
       <c r="V12" s="8"/>
       <c r="Y12" s="26"/>
     </row>
-    <row r="13" spans="1:31" ht="13.2">
+    <row r="13" spans="1:28" ht="13.2">
       <c r="A13" s="6">
         <v>46078.568784780087</v>
       </c>
       <c r="B13" s="7">
         <v>485918</v>
       </c>
-      <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
         <v>54</v>
       </c>
@@ -2207,7 +2173,6 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
@@ -2217,14 +2182,13 @@
       <c r="U13" s="8"/>
       <c r="V13" s="8"/>
     </row>
-    <row r="14" spans="1:31" ht="13.2">
+    <row r="14" spans="1:28" ht="13.2">
       <c r="A14" s="6">
         <v>46078.617964687495</v>
       </c>
       <c r="B14" s="7">
         <v>535474</v>
       </c>
-      <c r="C14" s="8"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9" t="s">
         <v>55</v>
@@ -2241,7 +2205,6 @@
       <c r="K14" s="9"/>
       <c r="L14" s="8"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -2251,14 +2214,13 @@
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
     </row>
-    <row r="15" spans="1:31" ht="13.2">
+    <row r="15" spans="1:28" ht="13.2">
       <c r="A15" s="6">
         <v>46084.829316446761</v>
       </c>
       <c r="B15" s="7">
         <v>614230</v>
       </c>
-      <c r="C15" s="8"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
         <v>55</v>
@@ -2273,7 +2235,6 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
@@ -2283,14 +2244,13 @@
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
     </row>
-    <row r="16" spans="1:31" ht="16.2">
+    <row r="16" spans="1:28" ht="16.2">
       <c r="A16" s="6">
         <v>46080.639740115745</v>
       </c>
       <c r="B16" s="7">
         <v>572964</v>
       </c>
-      <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
         <v>54</v>
       </c>
@@ -2319,7 +2279,6 @@
       <c r="M16" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
@@ -2342,7 +2301,6 @@
       <c r="B17" s="7">
         <v>614230</v>
       </c>
-      <c r="C17" s="8"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9" t="s">
         <v>55</v>
@@ -2357,7 +2315,6 @@
       <c r="K17" s="9"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
@@ -2374,7 +2331,6 @@
       <c r="B18" s="7">
         <v>572990</v>
       </c>
-      <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
         <v>54</v>
       </c>
@@ -2403,7 +2359,6 @@
       <c r="M18" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
@@ -2426,7 +2381,6 @@
       <c r="B19" s="7">
         <v>667725</v>
       </c>
-      <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
         <v>54</v>
       </c>
@@ -2453,7 +2407,6 @@
       <c r="M19" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
@@ -2470,7 +2423,6 @@
       <c r="B20" s="7">
         <v>667790</v>
       </c>
-      <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
         <v>78</v>
       </c>
@@ -2499,7 +2451,6 @@
       <c r="M20" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
@@ -2516,7 +2467,6 @@
       <c r="B21" s="7">
         <v>667802</v>
       </c>
-      <c r="C21" s="8"/>
       <c r="D21" s="9" t="s">
         <v>54</v>
       </c>
@@ -2543,7 +2493,6 @@
       <c r="M21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -2560,7 +2509,6 @@
       <c r="B22" s="7">
         <v>667903</v>
       </c>
-      <c r="C22" s="8"/>
       <c r="D22" s="9" t="s">
         <v>54</v>
       </c>
@@ -2581,7 +2529,6 @@
         <v>83</v>
       </c>
       <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
@@ -2598,7 +2545,6 @@
       <c r="B23" s="7">
         <v>777829</v>
       </c>
-      <c r="C23" s="8"/>
       <c r="D23" s="9" t="s">
         <v>68</v>
       </c>
@@ -2627,7 +2573,6 @@
       <c r="M23" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="N23" s="8"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -2644,7 +2589,6 @@
       <c r="B24" s="7">
         <v>794418</v>
       </c>
-      <c r="C24" s="8"/>
       <c r="D24" s="9" t="s">
         <v>54</v>
       </c>
@@ -2671,7 +2615,6 @@
       <c r="M24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
@@ -2688,7 +2631,6 @@
       <c r="B25" s="7">
         <v>798140</v>
       </c>
-      <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
         <v>54</v>
       </c>
@@ -2713,7 +2655,6 @@
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
@@ -2736,7 +2677,6 @@
       <c r="B26" s="7">
         <v>813903</v>
       </c>
-      <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
         <v>54</v>
       </c>
@@ -2763,7 +2703,6 @@
       <c r="M26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
@@ -2786,7 +2725,6 @@
       <c r="B27" s="7">
         <v>813927</v>
       </c>
-      <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
         <v>54</v>
       </c>
@@ -2815,7 +2753,6 @@
       <c r="M27" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
@@ -2832,7 +2769,6 @@
       <c r="B28" s="7">
         <v>919946</v>
       </c>
-      <c r="C28" s="8"/>
       <c r="D28" s="8" t="s">
         <v>54</v>
       </c>
@@ -2859,7 +2795,6 @@
       <c r="M28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
@@ -2876,7 +2811,6 @@
       <c r="B29" s="7">
         <v>919946</v>
       </c>
-      <c r="C29" s="8"/>
       <c r="D29" s="8" t="s">
         <v>54</v>
       </c>
@@ -2903,7 +2837,6 @@
       <c r="M29" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N29" s="8"/>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
@@ -2921,7 +2854,6 @@
       <c r="B30" s="7">
         <v>900151</v>
       </c>
-      <c r="C30" s="8"/>
       <c r="D30" s="8" t="s">
         <v>68</v>
       </c>
@@ -2942,7 +2874,6 @@
       <c r="M30" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="N30" s="8"/>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
@@ -2959,7 +2890,6 @@
       <c r="B31" s="7">
         <v>919959</v>
       </c>
-      <c r="C31" s="8"/>
       <c r="D31" s="8" t="s">
         <v>54</v>
       </c>
@@ -2980,7 +2910,6 @@
       <c r="M31" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="N31" s="8"/>
       <c r="O31" s="8"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
@@ -2997,7 +2926,6 @@
       <c r="B32" s="7">
         <v>926814</v>
       </c>
-      <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
         <v>54</v>
       </c>
@@ -3022,7 +2950,6 @@
       <c r="M32" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="N32" s="8"/>
       <c r="O32" s="8"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="8"/>
@@ -3367,7 +3294,6 @@
       <c r="B71" s="12">
         <v>926865</v>
       </c>
-      <c r="C71" s="8"/>
       <c r="D71" s="8" t="s">
         <v>54</v>
       </c>
@@ -3394,7 +3320,6 @@
       <c r="M71" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="N71" s="8"/>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
@@ -3411,7 +3336,6 @@
       <c r="B72" s="12">
         <v>926927</v>
       </c>
-      <c r="C72" s="8"/>
       <c r="D72" s="8" t="s">
         <v>54</v>
       </c>
@@ -3434,7 +3358,6 @@
       <c r="M72" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N72" s="8"/>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
@@ -3451,7 +3374,6 @@
       <c r="B73" s="12">
         <v>926941</v>
       </c>
-      <c r="C73" s="8"/>
       <c r="D73" s="8" t="s">
         <v>54</v>
       </c>
@@ -3476,7 +3398,6 @@
       <c r="M73" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N73" s="8"/>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
@@ -3493,7 +3414,6 @@
       <c r="B74" s="12">
         <v>926826</v>
       </c>
-      <c r="C74" s="8"/>
       <c r="D74" s="8" t="s">
         <v>54</v>
       </c>
@@ -3518,7 +3438,6 @@
       <c r="M74" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="N74" s="8"/>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
       <c r="Q74" s="8"/>
@@ -3535,7 +3454,6 @@
       <c r="B75" s="12">
         <v>965552</v>
       </c>
-      <c r="C75" s="8"/>
       <c r="D75" s="8" t="s">
         <v>68</v>
       </c>
@@ -3556,7 +3474,6 @@
       <c r="M75" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="N75" s="8"/>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
       <c r="Q75" s="8"/>
@@ -3573,7 +3490,6 @@
       <c r="B76" s="12">
         <v>965552</v>
       </c>
-      <c r="C76" s="8"/>
       <c r="D76" s="8" t="s">
         <v>68</v>
       </c>
@@ -3594,7 +3510,6 @@
       <c r="M76" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="N76" s="8"/>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
       <c r="Q76" s="8"/>
@@ -3611,7 +3526,6 @@
       <c r="B77" s="12">
         <v>956502</v>
       </c>
-      <c r="C77" s="8"/>
       <c r="D77" s="8" t="s">
         <v>54</v>
       </c>
@@ -3632,7 +3546,6 @@
       <c r="M77" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N77" s="8"/>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
       <c r="Q77" s="8"/>
@@ -3649,7 +3562,6 @@
       <c r="B78" s="12">
         <v>958658</v>
       </c>
-      <c r="C78" s="8"/>
       <c r="D78" s="8" t="s">
         <v>54</v>
       </c>
@@ -3672,7 +3584,6 @@
       <c r="M78" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N78" s="8"/>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
       <c r="Q78" s="8"/>
@@ -3689,7 +3600,6 @@
       <c r="B79" s="12">
         <v>965552</v>
       </c>
-      <c r="C79" s="8"/>
       <c r="D79" s="8" t="s">
         <v>68</v>
       </c>
@@ -3710,7 +3620,6 @@
       <c r="M79" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="N79" s="8"/>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
       <c r="Q79" s="8"/>
@@ -3727,7 +3636,6 @@
       <c r="B80" s="12">
         <v>977316</v>
       </c>
-      <c r="C80" s="8"/>
       <c r="D80" s="8" t="s">
         <v>119</v>
       </c>
@@ -3748,7 +3656,6 @@
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
       <c r="M80" s="8"/>
-      <c r="N80" s="8"/>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
       <c r="Q80" s="8"/>
@@ -3758,14 +3665,13 @@
       <c r="U80" s="8"/>
       <c r="V80" s="8"/>
     </row>
-    <row r="81" spans="1:31" ht="16.2">
+    <row r="81" spans="1:28" ht="16.2">
       <c r="A81" s="6">
         <v>46080.641628287034</v>
       </c>
       <c r="B81" s="12">
         <v>964698</v>
       </c>
-      <c r="C81" s="8"/>
       <c r="D81" s="8" t="s">
         <v>54</v>
       </c>
@@ -3786,7 +3692,6 @@
       <c r="M81" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N81" s="8"/>
       <c r="O81" s="8"/>
       <c r="P81" s="8"/>
       <c r="Q81" s="8"/>
@@ -3802,14 +3707,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="13.2">
+    <row r="82" spans="1:28" ht="13.2">
       <c r="A82" s="6">
         <v>46078.534898900463</v>
       </c>
       <c r="B82" s="12">
         <v>969081</v>
       </c>
-      <c r="C82" s="8"/>
       <c r="D82" s="8" t="s">
         <v>54</v>
       </c>
@@ -3828,7 +3732,6 @@
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
       <c r="M82" s="8"/>
-      <c r="N82" s="8"/>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
       <c r="Q82" s="8"/>
@@ -3838,14 +3741,13 @@
       <c r="U82" s="8"/>
       <c r="V82" s="8"/>
     </row>
-    <row r="83" spans="1:31" ht="13.2">
+    <row r="83" spans="1:28" ht="13.2">
       <c r="A83" s="6">
         <v>46086.336962430556</v>
       </c>
       <c r="B83" s="12">
         <v>969081</v>
       </c>
-      <c r="C83" s="8"/>
       <c r="D83" s="8" t="s">
         <v>54</v>
       </c>
@@ -3864,7 +3766,6 @@
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
       <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="8"/>
@@ -3874,14 +3775,13 @@
       <c r="U83" s="8"/>
       <c r="V83" s="8"/>
     </row>
-    <row r="84" spans="1:31" ht="13.2">
+    <row r="84" spans="1:28" ht="13.2">
       <c r="A84" s="6">
         <v>46084.801018819446</v>
       </c>
       <c r="B84" s="12">
         <v>977316</v>
       </c>
-      <c r="C84" s="8"/>
       <c r="D84" s="8" t="s">
         <v>119</v>
       </c>
@@ -3902,7 +3802,6 @@
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
       <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
       <c r="O84" s="8"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
@@ -3912,14 +3811,13 @@
       <c r="U84" s="8"/>
       <c r="V84" s="8"/>
     </row>
-    <row r="85" spans="1:31" ht="13.2">
+    <row r="85" spans="1:28" ht="13.2">
       <c r="A85" s="6">
         <v>46079.435836782402</v>
       </c>
       <c r="B85" s="12">
         <v>995225</v>
       </c>
-      <c r="C85" s="8"/>
       <c r="D85" s="8" t="s">
         <v>85</v>
       </c>
@@ -3936,7 +3834,6 @@
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
       <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
       <c r="Q85" s="8"/>
@@ -3946,59 +3843,59 @@
       <c r="U85" s="8"/>
       <c r="V85" s="8"/>
     </row>
-    <row r="86" spans="1:31" ht="15.75" customHeight="1">
+    <row r="86" spans="1:28" ht="15.75" customHeight="1">
       <c r="B86" s="12">
         <v>926941</v>
       </c>
-      <c r="AC86" s="28" t="s">
+      <c r="AA86" s="28" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="15.75" customHeight="1">
+    <row r="87" spans="1:28" ht="15.75" customHeight="1">
       <c r="B87" s="12">
         <v>964698</v>
       </c>
-      <c r="AC87" s="28" t="s">
+      <c r="AA87" s="28" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="15.75" customHeight="1">
+    <row r="88" spans="1:28" ht="15.75" customHeight="1">
       <c r="B88" s="12">
         <v>121172</v>
       </c>
-      <c r="AD88" s="28" t="s">
+      <c r="N88" s="28" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="15.75" customHeight="1">
+    <row r="89" spans="1:28" ht="15.75" customHeight="1">
       <c r="B89" s="32">
         <v>919946</v>
       </c>
-      <c r="AE89" s="31" t="s">
+      <c r="C89" s="31" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="15.75" customHeight="1">
+    <row r="90" spans="1:28" ht="15.75" customHeight="1">
       <c r="B90" s="32">
         <v>159297</v>
       </c>
-      <c r="AE90" s="31" t="s">
+      <c r="C90" s="31" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="15.75" customHeight="1">
+    <row r="91" spans="1:28" ht="15.75" customHeight="1">
       <c r="B91" s="32">
         <v>613493</v>
       </c>
-      <c r="AE91" s="31" t="s">
+      <c r="C91" s="31" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="15.75" customHeight="1">
+    <row r="92" spans="1:28" ht="15.75" customHeight="1">
       <c r="B92" s="32">
         <v>900151</v>
       </c>
-      <c r="AE92" s="31" t="s">
+      <c r="C92" s="31" t="s">
         <v>176</v>
       </c>
     </row>

--- a/data/問卷系統_月曆顯示.xlsx
+++ b/data/問卷系統_月曆顯示.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\271003\Desktop\Claude Office\工安自辦訓練表格填寫\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84743BD2-D967-44A2-8F88-ABD319121CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93371A1E-5553-4FD4-AB13-F59A07A7D477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="170">
   <si>
     <t>代碼</t>
   </si>
@@ -542,140 +542,6 @@
   </si>
   <si>
     <t>規劃赴大陸探親(7/18 ~ 8/3)</t>
-  </si>
-  <si>
-    <t>交通安全講習</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>8/24 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>上午</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft JhengHei"/>
-        <charset val="136"/>
-      </rPr>
-      <t>職業安全衛生委員會成員</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft JhengHei"/>
-        <charset val="136"/>
-      </rPr>
-      <t>在職教育訓練</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>9/2 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>上午</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>危害辨識</t>
-  </si>
-  <si>
-    <r>
-      <t>8/19 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>上午</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>8/26 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>上午</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -686,7 +552,7 @@
     <numFmt numFmtId="176" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="177" formatCode="m/d"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -750,26 +616,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft JhengHei"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -787,6 +633,13 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -874,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -937,15 +790,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1572,6 +1424,8 @@
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="24.33203125" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" customWidth="1"/>
+    <col min="14" max="14" width="34.33203125" style="32" customWidth="1"/>
+    <col min="27" max="27" width="12.6640625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="15.75" customHeight="1">
@@ -1581,8 +1435,8 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29" t="s">
-        <v>174</v>
+      <c r="C1" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>29</v>
@@ -1614,8 +1468,8 @@
       <c r="M1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="30" t="s">
-        <v>172</v>
+      <c r="N1" s="33" t="s">
+        <v>39</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>40</v>
@@ -1653,8 +1507,8 @@
       <c r="Z1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AA1" s="27" t="s">
-        <v>170</v>
+      <c r="AA1" s="30" t="s">
+        <v>52</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>53</v>
@@ -1693,6 +1547,7 @@
       <c r="M2" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="N2" s="31"/>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
@@ -1735,6 +1590,7 @@
       <c r="M3" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="N3" s="31"/>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
@@ -1779,6 +1635,7 @@
       <c r="M4" s="9" t="s">
         <v>65</v>
       </c>
+      <c r="N4" s="31"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
@@ -1823,6 +1680,7 @@
       <c r="M5" s="9" t="s">
         <v>60</v>
       </c>
+      <c r="N5" s="31"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
@@ -1867,6 +1725,7 @@
       <c r="M6" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="N6" s="31"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
@@ -1918,6 +1777,7 @@
       <c r="M7" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="N7" s="31"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
@@ -1960,6 +1820,7 @@
       <c r="M8" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="N8" s="31"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
@@ -2008,6 +1869,7 @@
       </c>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
+      <c r="N9" s="31"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
@@ -2044,6 +1906,7 @@
       <c r="K10" s="8"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
+      <c r="N10" s="31"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
@@ -2086,6 +1949,7 @@
       <c r="M11" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="N11" s="31"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
@@ -2136,6 +2000,7 @@
         <v>82</v>
       </c>
       <c r="M12" s="9"/>
+      <c r="N12" s="31"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
@@ -2173,6 +2038,7 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
+      <c r="N13" s="31"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
@@ -2205,6 +2071,7 @@
       <c r="K14" s="9"/>
       <c r="L14" s="8"/>
       <c r="M14" s="9"/>
+      <c r="N14" s="31"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -2235,6 +2102,7 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
+      <c r="N15" s="31"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
@@ -2279,6 +2147,7 @@
       <c r="M16" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N16" s="31"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
@@ -2315,6 +2184,7 @@
       <c r="K17" s="9"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
+      <c r="N17" s="31"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
@@ -2359,6 +2229,7 @@
       <c r="M18" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N18" s="31"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
@@ -2407,6 +2278,7 @@
       <c r="M19" s="8" t="s">
         <v>77</v>
       </c>
+      <c r="N19" s="31"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
@@ -2451,6 +2323,7 @@
       <c r="M20" s="9" t="s">
         <v>77</v>
       </c>
+      <c r="N20" s="31"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
@@ -2493,6 +2366,7 @@
       <c r="M21" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="N21" s="31"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -2529,6 +2403,7 @@
         <v>83</v>
       </c>
       <c r="M22" s="8"/>
+      <c r="N22" s="31"/>
       <c r="O22" s="8"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
@@ -2573,6 +2448,7 @@
       <c r="M23" s="9" t="s">
         <v>71</v>
       </c>
+      <c r="N23" s="31"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -2615,6 +2491,7 @@
       <c r="M24" s="9" t="s">
         <v>58</v>
       </c>
+      <c r="N24" s="31"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
@@ -2655,6 +2532,7 @@
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
+      <c r="N25" s="31"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
@@ -2703,6 +2581,7 @@
       <c r="M26" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N26" s="31"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
@@ -2753,6 +2632,7 @@
       <c r="M27" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N27" s="31"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
@@ -2795,6 +2675,7 @@
       <c r="M28" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N28" s="31"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
@@ -2837,6 +2718,7 @@
       <c r="M29" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N29" s="31"/>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
@@ -2874,6 +2756,7 @@
       <c r="M30" s="8" t="s">
         <v>60</v>
       </c>
+      <c r="N30" s="31"/>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
@@ -2910,6 +2793,7 @@
       <c r="M31" s="8" t="s">
         <v>60</v>
       </c>
+      <c r="N31" s="31"/>
       <c r="O31" s="8"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
@@ -2950,6 +2834,7 @@
       <c r="M32" s="8" t="s">
         <v>80</v>
       </c>
+      <c r="N32" s="31"/>
       <c r="O32" s="8"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="8"/>
@@ -3320,6 +3205,7 @@
       <c r="M71" s="8" t="s">
         <v>65</v>
       </c>
+      <c r="N71" s="31"/>
       <c r="O71" s="8"/>
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
@@ -3358,6 +3244,7 @@
       <c r="M72" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N72" s="31"/>
       <c r="O72" s="8"/>
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
@@ -3398,6 +3285,7 @@
       <c r="M73" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N73" s="31"/>
       <c r="O73" s="8"/>
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
@@ -3438,6 +3326,7 @@
       <c r="M74" s="8" t="s">
         <v>77</v>
       </c>
+      <c r="N74" s="31"/>
       <c r="O74" s="8"/>
       <c r="P74" s="8"/>
       <c r="Q74" s="8"/>
@@ -3474,6 +3363,7 @@
       <c r="M75" s="8" t="s">
         <v>65</v>
       </c>
+      <c r="N75" s="31"/>
       <c r="O75" s="8"/>
       <c r="P75" s="8"/>
       <c r="Q75" s="8"/>
@@ -3510,6 +3400,7 @@
       <c r="M76" s="8" t="s">
         <v>65</v>
       </c>
+      <c r="N76" s="31"/>
       <c r="O76" s="8"/>
       <c r="P76" s="8"/>
       <c r="Q76" s="8"/>
@@ -3546,6 +3437,7 @@
       <c r="M77" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N77" s="31"/>
       <c r="O77" s="8"/>
       <c r="P77" s="8"/>
       <c r="Q77" s="8"/>
@@ -3584,6 +3476,7 @@
       <c r="M78" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N78" s="31"/>
       <c r="O78" s="8"/>
       <c r="P78" s="8"/>
       <c r="Q78" s="8"/>
@@ -3620,6 +3513,7 @@
       <c r="M79" s="8" t="s">
         <v>65</v>
       </c>
+      <c r="N79" s="31"/>
       <c r="O79" s="8"/>
       <c r="P79" s="8"/>
       <c r="Q79" s="8"/>
@@ -3656,6 +3550,7 @@
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
       <c r="M80" s="8"/>
+      <c r="N80" s="31"/>
       <c r="O80" s="8"/>
       <c r="P80" s="8"/>
       <c r="Q80" s="8"/>
@@ -3692,6 +3587,7 @@
       <c r="M81" s="8" t="s">
         <v>58</v>
       </c>
+      <c r="N81" s="31"/>
       <c r="O81" s="8"/>
       <c r="P81" s="8"/>
       <c r="Q81" s="8"/>
@@ -3732,6 +3628,7 @@
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
       <c r="M82" s="8"/>
+      <c r="N82" s="31"/>
       <c r="O82" s="8"/>
       <c r="P82" s="8"/>
       <c r="Q82" s="8"/>
@@ -3766,6 +3663,7 @@
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
       <c r="M83" s="8"/>
+      <c r="N83" s="31"/>
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="8"/>
@@ -3802,6 +3700,7 @@
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
       <c r="M84" s="8"/>
+      <c r="N84" s="31"/>
       <c r="O84" s="8"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8"/>
@@ -3834,6 +3733,7 @@
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
       <c r="M85" s="8"/>
+      <c r="N85" s="31"/>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
       <c r="Q85" s="8"/>
@@ -3847,57 +3747,40 @@
       <c r="B86" s="12">
         <v>926941</v>
       </c>
-      <c r="AA86" s="28" t="s">
-        <v>171</v>
-      </c>
     </row>
     <row r="87" spans="1:28" ht="15.75" customHeight="1">
       <c r="B87" s="12">
         <v>964698</v>
       </c>
-      <c r="AA87" s="28" t="s">
-        <v>171</v>
-      </c>
     </row>
     <row r="88" spans="1:28" ht="15.75" customHeight="1">
       <c r="B88" s="12">
         <v>121172</v>
       </c>
-      <c r="N88" s="28" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="89" spans="1:28" ht="15.75" customHeight="1">
-      <c r="B89" s="32">
+      <c r="B89" s="29">
         <v>919946</v>
       </c>
-      <c r="C89" s="31" t="s">
-        <v>175</v>
-      </c>
+      <c r="C89" s="28"/>
     </row>
     <row r="90" spans="1:28" ht="15.75" customHeight="1">
-      <c r="B90" s="32">
+      <c r="B90" s="29">
         <v>159297</v>
       </c>
-      <c r="C90" s="31" t="s">
-        <v>175</v>
-      </c>
+      <c r="C90" s="28"/>
     </row>
     <row r="91" spans="1:28" ht="15.75" customHeight="1">
-      <c r="B91" s="32">
+      <c r="B91" s="29">
         <v>613493</v>
       </c>
-      <c r="C91" s="31" t="s">
-        <v>176</v>
-      </c>
+      <c r="C91" s="28"/>
     </row>
     <row r="92" spans="1:28" ht="15.75" customHeight="1">
-      <c r="B92" s="32">
+      <c r="B92" s="29">
         <v>900151</v>
       </c>
-      <c r="C92" s="31" t="s">
-        <v>176</v>
-      </c>
+      <c r="C92" s="28"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB91">

--- a/data/問卷系統_月曆顯示.xlsx
+++ b/data/問卷系統_月曆顯示.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\271003\Desktop\Claude Office\工安自辦訓練表格填寫\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93371A1E-5553-4FD4-AB13-F59A07A7D477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB1965-11DD-4054-9432-5C7F6A73B30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="177">
   <si>
     <t>代碼</t>
   </si>
@@ -542,6 +542,141 @@
   </si>
   <si>
     <t>規劃赴大陸探親(7/18 ~ 8/3)</t>
+  </si>
+  <si>
+    <t>危害辨識</t>
+  </si>
+  <si>
+    <r>
+      <t>8/19 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上午</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8/26 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上午</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <charset val="136"/>
+      </rPr>
+      <t>職業安全衛生委員會成員</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <charset val="136"/>
+      </rPr>
+      <t>在職教育訓練</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>9/2 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上午</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>交通安全講習</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8/24 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上午</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -552,7 +687,7 @@
     <numFmt numFmtId="176" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="177" formatCode="m/d"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -563,6 +698,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -640,6 +776,26 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="6">
@@ -727,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -798,6 +954,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1410,25 +1572,30 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AB92"/>
+  <dimension ref="A1:AE92"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" customWidth="1"/>
     <col min="8" max="8" width="9.109375" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="24.33203125" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" customWidth="1"/>
     <col min="14" max="14" width="34.33203125" style="32" customWidth="1"/>
-    <col min="27" max="27" width="12.6640625" style="32"/>
+    <col min="15" max="26" width="12.6640625" customWidth="1"/>
+    <col min="27" max="27" width="12.6640625" style="32" customWidth="1"/>
+    <col min="28" max="28" width="12.6640625" customWidth="1"/>
+    <col min="29" max="31" width="12.6640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <row r="1" spans="1:31" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1513,8 +1680,17 @@
       <c r="AB1" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" ht="13.2">
+      <c r="AC1" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="AD1" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE1" s="37" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" ht="13.2">
       <c r="A2" s="6">
         <v>46079.470154050927</v>
       </c>
@@ -1557,7 +1733,7 @@
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
     </row>
-    <row r="3" spans="1:28" ht="13.2">
+    <row r="3" spans="1:31" ht="13.2">
       <c r="A3" s="6">
         <v>46078.495963310183</v>
       </c>
@@ -1600,7 +1776,7 @@
       <c r="U3" s="8"/>
       <c r="V3" s="8"/>
     </row>
-    <row r="4" spans="1:28" ht="13.2">
+    <row r="4" spans="1:31" ht="13.2">
       <c r="A4" s="6">
         <v>46078.667671388888</v>
       </c>
@@ -1645,7 +1821,7 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
     </row>
-    <row r="5" spans="1:28" ht="13.2">
+    <row r="5" spans="1:31" ht="13.2">
       <c r="A5" s="6">
         <v>46078.497951516205</v>
       </c>
@@ -1690,7 +1866,7 @@
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
     </row>
-    <row r="6" spans="1:28" ht="16.2">
+    <row r="6" spans="1:31" ht="16.2">
       <c r="A6" s="6">
         <v>46080.643336354166</v>
       </c>
@@ -1744,7 +1920,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="13.2">
+    <row r="7" spans="1:31" ht="13.2">
       <c r="A7" s="6">
         <v>46078.564764513889</v>
       </c>
@@ -1787,7 +1963,7 @@
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
-    <row r="8" spans="1:28" ht="16.2">
+    <row r="8" spans="1:31" ht="16.2">
       <c r="A8" s="6">
         <v>46083.037832708331</v>
       </c>
@@ -1836,7 +2012,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="13.2">
+    <row r="9" spans="1:31" ht="13.2">
       <c r="A9" s="6">
         <v>46078.574391724542</v>
       </c>
@@ -1879,7 +2055,7 @@
       <c r="U9" s="8"/>
       <c r="V9" s="8"/>
     </row>
-    <row r="10" spans="1:28" ht="13.2">
+    <row r="10" spans="1:31" ht="13.2">
       <c r="A10" s="6">
         <v>46084.843648472219</v>
       </c>
@@ -1916,7 +2092,7 @@
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
     </row>
-    <row r="11" spans="1:28" ht="16.2">
+    <row r="11" spans="1:31" ht="16.2">
       <c r="A11" s="6">
         <v>46083.037841921294</v>
       </c>
@@ -1965,7 +2141,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="13.2">
+    <row r="12" spans="1:31" ht="13.2">
       <c r="A12" s="6">
         <v>46078.568878067133</v>
       </c>
@@ -2011,7 +2187,7 @@
       <c r="V12" s="8"/>
       <c r="Y12" s="26"/>
     </row>
-    <row r="13" spans="1:28" ht="13.2">
+    <row r="13" spans="1:31" ht="13.2">
       <c r="A13" s="6">
         <v>46078.568784780087</v>
       </c>
@@ -2048,7 +2224,7 @@
       <c r="U13" s="8"/>
       <c r="V13" s="8"/>
     </row>
-    <row r="14" spans="1:28" ht="13.2">
+    <row r="14" spans="1:31" ht="13.2">
       <c r="A14" s="6">
         <v>46078.617964687495</v>
       </c>
@@ -2081,7 +2257,7 @@
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
     </row>
-    <row r="15" spans="1:28" ht="13.2">
+    <row r="15" spans="1:31" ht="13.2">
       <c r="A15" s="6">
         <v>46084.829316446761</v>
       </c>
@@ -2112,7 +2288,7 @@
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
     </row>
-    <row r="16" spans="1:28" ht="16.2">
+    <row r="16" spans="1:31" ht="16.2">
       <c r="A16" s="6">
         <v>46080.639740115745</v>
       </c>
@@ -3560,7 +3736,7 @@
       <c r="U80" s="8"/>
       <c r="V80" s="8"/>
     </row>
-    <row r="81" spans="1:28" ht="16.2">
+    <row r="81" spans="1:31" ht="16.2">
       <c r="A81" s="6">
         <v>46080.641628287034</v>
       </c>
@@ -3603,7 +3779,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="82" spans="1:28" ht="13.2">
+    <row r="82" spans="1:31" ht="13.2">
       <c r="A82" s="6">
         <v>46078.534898900463</v>
       </c>
@@ -3638,7 +3814,7 @@
       <c r="U82" s="8"/>
       <c r="V82" s="8"/>
     </row>
-    <row r="83" spans="1:28" ht="13.2">
+    <row r="83" spans="1:31" ht="13.2">
       <c r="A83" s="6">
         <v>46086.336962430556</v>
       </c>
@@ -3673,7 +3849,7 @@
       <c r="U83" s="8"/>
       <c r="V83" s="8"/>
     </row>
-    <row r="84" spans="1:28" ht="13.2">
+    <row r="84" spans="1:31" ht="13.2">
       <c r="A84" s="6">
         <v>46084.801018819446</v>
       </c>
@@ -3710,7 +3886,7 @@
       <c r="U84" s="8"/>
       <c r="V84" s="8"/>
     </row>
-    <row r="85" spans="1:28" ht="13.2">
+    <row r="85" spans="1:31" ht="13.2">
       <c r="A85" s="6">
         <v>46079.435836782402</v>
       </c>
@@ -3743,44 +3919,65 @@
       <c r="U85" s="8"/>
       <c r="V85" s="8"/>
     </row>
-    <row r="86" spans="1:28" ht="15.75" customHeight="1">
+    <row r="86" spans="1:31" ht="15.75" customHeight="1">
       <c r="B86" s="12">
         <v>926941</v>
       </c>
-    </row>
-    <row r="87" spans="1:28" ht="15.75" customHeight="1">
+      <c r="AE86" s="36" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="87" spans="1:31" ht="15.75" customHeight="1">
       <c r="B87" s="12">
         <v>964698</v>
       </c>
-    </row>
-    <row r="88" spans="1:28" ht="15.75" customHeight="1">
+      <c r="AE87" s="36" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" spans="1:31" ht="15.75" customHeight="1">
       <c r="B88" s="12">
         <v>121172</v>
       </c>
-    </row>
-    <row r="89" spans="1:28" ht="15.75" customHeight="1">
+      <c r="AD88" s="36" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="89" spans="1:31" ht="15.75" customHeight="1">
       <c r="B89" s="29">
         <v>919946</v>
       </c>
       <c r="C89" s="28"/>
-    </row>
-    <row r="90" spans="1:28" ht="15.75" customHeight="1">
+      <c r="AC89" s="28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="90" spans="1:31" ht="15.75" customHeight="1">
       <c r="B90" s="29">
         <v>159297</v>
       </c>
       <c r="C90" s="28"/>
-    </row>
-    <row r="91" spans="1:28" ht="15.75" customHeight="1">
+      <c r="AC90" s="28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="91" spans="1:31" ht="15.75" customHeight="1">
       <c r="B91" s="29">
         <v>613493</v>
       </c>
       <c r="C91" s="28"/>
-    </row>
-    <row r="92" spans="1:28" ht="15.75" customHeight="1">
+      <c r="AC91" s="28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="92" spans="1:31" ht="15.75" customHeight="1">
       <c r="B92" s="29">
         <v>900151</v>
       </c>
       <c r="C92" s="28"/>
+      <c r="AC92" s="28" t="s">
+        <v>172</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB91">

--- a/data/問卷系統_月曆顯示.xlsx
+++ b/data/問卷系統_月曆顯示.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\271003\Desktop\Claude Office\工安自辦訓練表格填寫\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e7512d0a0cfb7bd/公司電腦/^N研測課長業務/訓練排程上網/資料庫自動化雲端更新/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB1965-11DD-4054-9432-5C7F6A73B30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4FFB1965-11DD-4054-9432-5C7F6A73B30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D65399B-36C7-4BA1-AF2B-506EDE599D50}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="185">
   <si>
     <t>代碼</t>
   </si>
@@ -677,6 +677,30 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>2026/3/12 上午 10:53:13</t>
+  </si>
+  <si>
+    <t>7/8 (一天)</t>
+  </si>
+  <si>
+    <t>2026/3/12 上午 11:10:50</t>
+  </si>
+  <si>
+    <t>2026/3/12 上午 11:24:03</t>
+  </si>
+  <si>
+    <t>8/25 (上午)</t>
+  </si>
+  <si>
+    <t>2026/3/12 上午 11:25:06</t>
+  </si>
+  <si>
+    <t>2026/3/12 下午 1:12:35</t>
+  </si>
+  <si>
+    <t>2026/3/12 下午 3:27:59</t>
   </si>
 </sst>
 </file>
@@ -830,7 +854,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -879,11 +903,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -949,7 +999,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -960,6 +1009,50 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1572,27 +1665,39 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE92"/>
+  <dimension ref="A1:AE99"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="24.33203125" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" customWidth="1"/>
-    <col min="14" max="14" width="34.33203125" style="32" customWidth="1"/>
-    <col min="15" max="26" width="12.6640625" customWidth="1"/>
-    <col min="27" max="27" width="12.6640625" style="32" customWidth="1"/>
-    <col min="28" max="28" width="12.6640625" customWidth="1"/>
-    <col min="29" max="31" width="12.6640625" style="32"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="42.21875" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.6640625" style="31"/>
+    <col min="31" max="31" width="13.109375" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" customHeight="1">
@@ -1635,7 +1740,7 @@
       <c r="M1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="32" t="s">
         <v>39</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -1674,31 +1779,31 @@
       <c r="Z1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AA1" s="30" t="s">
+      <c r="AA1" s="29" t="s">
         <v>52</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AC1" s="34" t="s">
+      <c r="AC1" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="AD1" s="35" t="s">
+      <c r="AD1" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="AE1" s="37" t="s">
+      <c r="AE1" s="36" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="13.2">
       <c r="A2" s="6">
-        <v>46079.470154050927</v>
+        <v>46078.482949444442</v>
       </c>
       <c r="B2" s="7">
-        <v>121172</v>
+        <v>956502</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>55</v>
@@ -1707,23 +1812,17 @@
         <v>56</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>79</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H2" s="8"/>
       <c r="I2" s="8"/>
-      <c r="J2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>64</v>
-      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="31"/>
+      <c r="N2" s="30"/>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
@@ -1735,128 +1834,114 @@
     </row>
     <row r="3" spans="1:31" ht="13.2">
       <c r="A3" s="6">
-        <v>46078.495963310183</v>
-      </c>
-      <c r="B3" s="7">
-        <v>159297</v>
-      </c>
-      <c r="D3" s="9" t="s">
+        <v>46078.484767696762</v>
+      </c>
+      <c r="B3" s="46">
+        <v>919959</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="N3" s="31"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="30"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
     </row>
     <row r="4" spans="1:31" ht="13.2">
       <c r="A4" s="6">
-        <v>46078.667671388888</v>
-      </c>
-      <c r="B4" s="7">
-        <v>271003</v>
-      </c>
-      <c r="D4" s="9" t="s">
+        <v>46078.484849120374</v>
+      </c>
+      <c r="B4" s="12">
+        <v>926927</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="N4" s="31"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N4" s="30"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
     </row>
     <row r="5" spans="1:31" ht="13.2">
       <c r="A5" s="6">
-        <v>46078.497951516205</v>
-      </c>
-      <c r="B5" s="7">
-        <v>420048</v>
+        <v>46078.486714120372</v>
+      </c>
+      <c r="B5" s="46">
+        <v>926865</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="9"/>
+      <c r="G5" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="H5" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>74</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="I5" s="8"/>
       <c r="J5" s="9" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>76</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="L5" s="8"/>
       <c r="M5" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" s="31"/>
+        <v>65</v>
+      </c>
+      <c r="N5" s="30"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
@@ -1866,171 +1951,156 @@
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
     </row>
-    <row r="6" spans="1:31" ht="16.2">
+    <row r="6" spans="1:31" ht="13.2">
       <c r="A6" s="6">
-        <v>46080.643336354166</v>
-      </c>
-      <c r="B6" s="7">
-        <v>365700</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="9" t="s">
+        <v>46078.48830921296</v>
+      </c>
+      <c r="B6" s="46">
+        <v>667802</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="F6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="9" t="s">
+      <c r="K6" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="31"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="Y6" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z6" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>96</v>
-      </c>
+      <c r="N6" s="30"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="X6" s="26"/>
+      <c r="Y6" s="26"/>
     </row>
     <row r="7" spans="1:31" ht="13.2">
       <c r="A7" s="6">
-        <v>46078.564764513889</v>
-      </c>
-      <c r="B7" s="7">
-        <v>420099</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9" t="s">
+        <v>46078.490101053241</v>
+      </c>
+      <c r="B7" s="46">
+        <v>777829</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="N7" s="31"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-    </row>
-    <row r="8" spans="1:31" ht="16.2">
+      <c r="L7" s="10"/>
+      <c r="M7" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" s="30"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+    </row>
+    <row r="8" spans="1:31" ht="13.2">
       <c r="A8" s="6">
-        <v>46083.037832708331</v>
-      </c>
-      <c r="B8" s="7">
-        <v>424503</v>
-      </c>
-      <c r="D8" s="9" t="s">
+        <v>46078.495963310183</v>
+      </c>
+      <c r="B8" s="12">
+        <v>159297</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="9" t="s">
+      <c r="F8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="31"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="Z8" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="N8" s="30"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
     </row>
     <row r="9" spans="1:31" ht="13.2">
       <c r="A9" s="6">
-        <v>46078.574391724542</v>
+        <v>46078.497951516205</v>
       </c>
       <c r="B9" s="7">
-        <v>438515</v>
+        <v>420048</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>57</v>
-      </c>
+      <c r="G9" s="10"/>
       <c r="H9" s="9" t="s">
         <v>66</v>
       </c>
@@ -2038,14 +2108,18 @@
         <v>74</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="31"/>
+      <c r="L9" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="30"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
@@ -2057,47 +2131,51 @@
     </row>
     <row r="10" spans="1:31" ht="13.2">
       <c r="A10" s="6">
-        <v>46084.843648472219</v>
-      </c>
-      <c r="B10" s="7">
-        <v>440471</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="9" t="s">
+        <v>46078.500472997686</v>
+      </c>
+      <c r="B10" s="46">
+        <v>926826</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-    </row>
-    <row r="11" spans="1:31" ht="16.2">
+      <c r="K10" s="10"/>
+      <c r="L10" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N10" s="30"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+    </row>
+    <row r="11" spans="1:31" ht="13.2">
       <c r="A11" s="6">
-        <v>46083.037841921294</v>
-      </c>
-      <c r="B11" s="7">
-        <v>424503</v>
+        <v>46078.500563287038</v>
+      </c>
+      <c r="B11" s="46">
+        <v>813927</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>54</v>
@@ -2106,26 +2184,28 @@
         <v>55</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="8" t="s">
-        <v>69</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="8"/>
       <c r="J11" s="9" t="s">
         <v>61</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="9"/>
+        <v>67</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="M11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="N11" s="31"/>
+      <c r="N11" s="30"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
@@ -2134,28 +2214,22 @@
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
-      <c r="Z11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB11" s="1" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="12" spans="1:31" ht="13.2">
       <c r="A12" s="6">
-        <v>46078.568878067133</v>
-      </c>
-      <c r="B12" s="7">
-        <v>441802</v>
+        <v>46078.520614456022</v>
+      </c>
+      <c r="B12" s="46">
+        <v>667725</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>57</v>
@@ -2163,20 +2237,18 @@
       <c r="H12" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>74</v>
-      </c>
+      <c r="I12" s="8"/>
       <c r="J12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>81</v>
-      </c>
+      <c r="K12" s="8"/>
       <c r="L12" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="31"/>
+        <v>76</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="N12" s="30"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
@@ -2185,69 +2257,76 @@
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
       <c r="V12" s="8"/>
-      <c r="Y12" s="26"/>
     </row>
     <row r="13" spans="1:31" ht="13.2">
       <c r="A13" s="6">
-        <v>46078.568784780087</v>
-      </c>
-      <c r="B13" s="7">
-        <v>485918</v>
-      </c>
-      <c r="D13" s="9" t="s">
+        <v>46078.534898900463</v>
+      </c>
+      <c r="B13" s="12">
+        <v>969081</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="F13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
     </row>
     <row r="14" spans="1:31" ht="13.2">
       <c r="A14" s="6">
-        <v>46078.617964687495</v>
+        <v>46078.564764513889</v>
       </c>
       <c r="B14" s="7">
-        <v>535474</v>
-      </c>
-      <c r="D14" s="9"/>
+        <v>420099</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="E14" s="9" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="9"/>
+        <v>62</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="I14" s="8"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
+      <c r="J14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="L14" s="8"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="31"/>
+      <c r="M14" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="N14" s="30"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -2259,26 +2338,32 @@
     </row>
     <row r="15" spans="1:31" ht="13.2">
       <c r="A15" s="6">
-        <v>46084.829316446761</v>
+        <v>46078.568784780087</v>
       </c>
       <c r="B15" s="7">
-        <v>614230</v>
-      </c>
-      <c r="D15" s="9"/>
+        <v>485918</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="E15" s="9" t="s">
         <v>55</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+        <v>59</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="31"/>
+      <c r="N15" s="30"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
@@ -2288,21 +2373,21 @@
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
     </row>
-    <row r="16" spans="1:31" ht="16.2">
+    <row r="16" spans="1:31" ht="13.2">
       <c r="A16" s="6">
-        <v>46080.639740115745</v>
+        <v>46078.568878067133</v>
       </c>
       <c r="B16" s="7">
-        <v>572964</v>
+        <v>441802</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>57</v>
@@ -2311,19 +2396,19 @@
         <v>66</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>61</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N16" s="31"/>
+        <v>81</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" s="8"/>
+      <c r="N16" s="30"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
@@ -2332,35 +2417,42 @@
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
-      <c r="Z16" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB16" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="Y16" s="26"/>
     </row>
     <row r="17" spans="1:28" ht="13.2">
       <c r="A17" s="6">
-        <v>46084.829352060187</v>
+        <v>46078.574391724542</v>
       </c>
       <c r="B17" s="7">
-        <v>614230</v>
-      </c>
-      <c r="D17" s="9"/>
+        <v>438515</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="E17" s="9" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="G17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>67</v>
+      </c>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
-      <c r="N17" s="31"/>
+      <c r="N17" s="30"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
@@ -2370,67 +2462,51 @@
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
     </row>
-    <row r="18" spans="1:28" ht="16.2">
+    <row r="18" spans="1:28" ht="13.2">
       <c r="A18" s="6">
-        <v>46083.634491840276</v>
-      </c>
-      <c r="B18" s="7">
-        <v>572990</v>
-      </c>
-      <c r="D18" s="9" t="s">
+        <v>46078.578018553242</v>
+      </c>
+      <c r="B18" s="46">
+        <v>667903</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" s="9" t="s">
+      <c r="F18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N18" s="31"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="Z18" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB18" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M18" s="10"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
     </row>
     <row r="19" spans="1:28" ht="13.2">
       <c r="A19" s="6">
-        <v>46078.520614456022</v>
-      </c>
-      <c r="B19" s="7">
-        <v>667725</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>54</v>
-      </c>
+        <v>46078.617964687495</v>
+      </c>
+      <c r="B19" s="12">
+        <v>535474</v>
+      </c>
+      <c r="D19" s="8"/>
       <c r="E19" s="9" t="s">
         <v>55</v>
       </c>
@@ -2440,21 +2516,13 @@
       <c r="G19" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="J19" s="8"/>
       <c r="K19" s="8"/>
-      <c r="L19" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="N19" s="31"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="30"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
@@ -2466,55 +2534,49 @@
     </row>
     <row r="20" spans="1:28" ht="13.2">
       <c r="A20" s="6">
-        <v>46084.743685486115</v>
-      </c>
-      <c r="B20" s="7">
-        <v>667790</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="9" t="s">
+        <v>46078.651622349542</v>
+      </c>
+      <c r="B20" s="12">
+        <v>958658</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="9" t="s">
+      <c r="F20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="9" t="s">
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K20" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="L20" s="8"/>
-      <c r="M20" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="N20" s="31"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="30"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
     </row>
     <row r="21" spans="1:28" ht="13.2">
       <c r="A21" s="6">
-        <v>46078.48830921296</v>
+        <v>46078.667671388888</v>
       </c>
       <c r="B21" s="7">
-        <v>667802</v>
+        <v>271003</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>54</v>
@@ -2526,23 +2588,25 @@
         <v>56</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I21" s="9"/>
+      <c r="I21" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="J21" s="9" t="s">
         <v>61</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="L21" s="8"/>
       <c r="M21" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="N21" s="31"/>
+        <v>65</v>
+      </c>
+      <c r="N21" s="30"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -2553,51 +2617,48 @@
       <c r="V21" s="8"/>
     </row>
     <row r="22" spans="1:28" ht="13.2">
-      <c r="A22" s="6">
-        <v>46078.578018553242</v>
-      </c>
-      <c r="B22" s="7">
-        <v>667903</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="9" t="s">
+      <c r="A22" s="54">
+        <v>46079.435836782402</v>
+      </c>
+      <c r="B22" s="46">
+        <v>995225</v>
+      </c>
+      <c r="C22" s="26"/>
+      <c r="D22" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="9" t="s">
+      <c r="F22" s="52"/>
+      <c r="G22" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="M22" s="8"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="52"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="52"/>
+      <c r="U22" s="52"/>
+      <c r="V22" s="52"/>
     </row>
     <row r="23" spans="1:28" ht="13.2">
       <c r="A23" s="6">
-        <v>46078.490101053241</v>
+        <v>46079.449516863431</v>
       </c>
       <c r="B23" s="7">
-        <v>777829</v>
+        <v>926941</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>55</v>
@@ -2611,20 +2672,16 @@
       <c r="H23" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L23" s="9"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="M23" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="N23" s="31"/>
+        <v>58</v>
+      </c>
+      <c r="N23" s="30"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -2636,87 +2693,87 @@
     </row>
     <row r="24" spans="1:28" ht="13.2">
       <c r="A24" s="6">
-        <v>46084.738894351853</v>
-      </c>
-      <c r="B24" s="7">
-        <v>794418</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="9" t="s">
+        <v>46079.470154050927</v>
+      </c>
+      <c r="B24" s="12">
+        <v>121172</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="9" t="s">
+      <c r="G24" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K24" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="L24" s="8"/>
-      <c r="M24" s="9" t="s">
+      <c r="K24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="N24" s="31"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
     </row>
     <row r="25" spans="1:28" ht="16.2">
       <c r="A25" s="6">
         <v>46080.638196770829</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="46">
         <v>798140</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8" t="s">
+      <c r="I25" s="10"/>
+      <c r="J25" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="K25" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
       <c r="Z25" s="5" t="s">
         <v>88</v>
       </c>
@@ -2726,16 +2783,16 @@
     </row>
     <row r="26" spans="1:28" ht="16.2">
       <c r="A26" s="6">
-        <v>46080.642606666668</v>
+        <v>46080.639740115745</v>
       </c>
       <c r="B26" s="7">
-        <v>813903</v>
+        <v>572964</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>56</v>
@@ -2746,18 +2803,20 @@
       <c r="H26" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="I26" s="8"/>
+      <c r="I26" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="J26" s="8" t="s">
         <v>61</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N26" s="31"/>
+      <c r="N26" s="30"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
@@ -2767,63 +2826,61 @@
       <c r="U26" s="8"/>
       <c r="V26" s="8"/>
       <c r="Z26" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB26" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" ht="16.2">
+      <c r="A27" s="6">
+        <v>46080.641628287034</v>
+      </c>
+      <c r="B27" s="12">
+        <v>964698</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="30"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
+      <c r="V27" s="10"/>
+      <c r="Z27" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="AB26" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" ht="13.2">
-      <c r="A27" s="6">
-        <v>46078.500563287038</v>
-      </c>
-      <c r="B27" s="7">
-        <v>813927</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N27" s="31"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-    </row>
-    <row r="28" spans="1:28" ht="13.2">
+      <c r="AB27" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="16.2">
       <c r="A28" s="6">
-        <v>46084.736569953704</v>
-      </c>
-      <c r="B28" s="7">
-        <v>919946</v>
+        <v>46080.642606666668</v>
+      </c>
+      <c r="B28" s="46">
+        <v>813903</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>54</v>
@@ -2832,10 +2889,10 @@
         <v>73</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>66</v>
@@ -2845,13 +2902,13 @@
         <v>61</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="L28" s="8"/>
       <c r="M28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N28" s="31"/>
+      <c r="N28" s="30"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
@@ -2860,79 +2917,101 @@
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
-    </row>
-    <row r="29" spans="1:28" ht="13.2">
+      <c r="Z28" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" ht="16.2">
       <c r="A29" s="6">
-        <v>46084.73660635417</v>
-      </c>
-      <c r="B29" s="7">
-        <v>919946</v>
-      </c>
-      <c r="D29" s="8" t="s">
+        <v>46080.643336354166</v>
+      </c>
+      <c r="B29" s="12">
+        <v>365700</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N29" s="30"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="Y29" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB29" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" ht="16.2">
+      <c r="A30" s="6">
+        <v>46083.037832708331</v>
+      </c>
+      <c r="B30" s="7">
+        <v>424503</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="8" t="s">
+      <c r="E30" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G30" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8" t="s">
+      <c r="H30" s="8"/>
+      <c r="I30" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="K30" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N29" s="31"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
-      <c r="Y29" s="25"/>
-    </row>
-    <row r="30" spans="1:28" ht="13.2">
-      <c r="A30" s="6">
-        <v>46085.448310879627</v>
-      </c>
-      <c r="B30" s="7">
-        <v>900151</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="N30" s="31"/>
+        <v>58</v>
+      </c>
+      <c r="N30" s="30"/>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
@@ -2941,1047 +3020,1576 @@
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
-    </row>
-    <row r="31" spans="1:28" ht="13.2">
+      <c r="Z30" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB30" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" ht="16.2">
       <c r="A31" s="6">
-        <v>46078.484767696762</v>
-      </c>
-      <c r="B31" s="7">
-        <v>919959</v>
-      </c>
-      <c r="D31" s="8" t="s">
+        <v>46083.037841921294</v>
+      </c>
+      <c r="B31" s="12">
+        <v>424503</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="30"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="Z31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" ht="16.2">
+      <c r="A32" s="6">
+        <v>46083.634491840276</v>
+      </c>
+      <c r="B32" s="12">
+        <v>572990</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8" t="s">
+      <c r="H32" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="30"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10"/>
+      <c r="V32" s="10"/>
+      <c r="Z32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB32" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="13.2">
+      <c r="A33" s="6">
+        <v>46084.736569953704</v>
+      </c>
+      <c r="B33" s="38">
+        <v>919946</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" s="30"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+    </row>
+    <row r="34" spans="1:25" ht="13.2">
+      <c r="A34" s="6">
+        <v>46084.73660635417</v>
+      </c>
+      <c r="B34" s="38">
+        <v>919946</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="30"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="Y34" s="26"/>
+    </row>
+    <row r="35" spans="1:25" ht="13.2">
+      <c r="A35" s="6">
+        <v>46084.738894351853</v>
+      </c>
+      <c r="B35" s="38">
+        <v>794418</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N35" s="30"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="39"/>
+    </row>
+    <row r="36" spans="1:25" ht="13.2">
+      <c r="A36" s="6">
+        <v>46084.742802141205</v>
+      </c>
+      <c r="B36" s="38">
+        <v>965552</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N36" s="30"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="39"/>
+    </row>
+    <row r="37" spans="1:25" ht="13.2">
+      <c r="A37" s="6">
+        <v>46084.742829363429</v>
+      </c>
+      <c r="B37" s="38">
+        <v>965552</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N37" s="30"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
+      <c r="V37" s="39"/>
+    </row>
+    <row r="38" spans="1:25" ht="13.2">
+      <c r="A38" s="6">
+        <v>46084.742841701387</v>
+      </c>
+      <c r="B38" s="38">
+        <v>965552</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N38" s="30"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="39"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
+      <c r="U38" s="10"/>
+      <c r="V38" s="10"/>
+    </row>
+    <row r="39" spans="1:25" ht="13.2">
+      <c r="A39" s="6">
+        <v>46084.743685486115</v>
+      </c>
+      <c r="B39" s="38">
+        <v>667790</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N39" s="30"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="39"/>
+      <c r="U39" s="10"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="25"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="26"/>
+    </row>
+    <row r="40" spans="1:25" ht="13.2">
+      <c r="A40" s="6">
+        <v>46084.76020355324</v>
+      </c>
+      <c r="B40" s="38">
+        <v>926814</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M40" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N40" s="30"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+    </row>
+    <row r="41" spans="1:25" ht="13.2">
+      <c r="A41" s="6">
+        <v>46084.800993645833</v>
+      </c>
+      <c r="B41" s="38">
+        <v>977316</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
+      <c r="V41" s="10"/>
+      <c r="Y41" s="25"/>
+    </row>
+    <row r="42" spans="1:25" ht="13.2">
+      <c r="A42" s="54">
+        <v>46084.801018819446</v>
+      </c>
+      <c r="B42" s="38">
+        <v>977316</v>
+      </c>
+      <c r="C42" s="26"/>
+      <c r="D42" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="E42" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="F42" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="H42" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="52"/>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="52"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="52"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="52"/>
+      <c r="Y42" s="25"/>
+    </row>
+    <row r="43" spans="1:25" ht="13.2">
+      <c r="A43" s="6">
+        <v>46084.829316446761</v>
+      </c>
+      <c r="B43" s="38">
+        <v>614230</v>
+      </c>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
+      <c r="V43" s="52"/>
+      <c r="X43" s="25"/>
+      <c r="Y43" s="25"/>
+    </row>
+    <row r="44" spans="1:25" ht="13.2">
+      <c r="A44" s="6">
+        <v>46084.829352060187</v>
+      </c>
+      <c r="B44" s="38">
+        <v>614230</v>
+      </c>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
+      <c r="U44" s="10"/>
+      <c r="V44" s="52"/>
+    </row>
+    <row r="45" spans="1:25" ht="13.2">
+      <c r="A45" s="6">
+        <v>46084.843648472219</v>
+      </c>
+      <c r="B45" s="38">
+        <v>440471</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
+    </row>
+    <row r="46" spans="1:25" ht="13.2">
+      <c r="A46" s="6">
+        <v>46085.448310879627</v>
+      </c>
+      <c r="B46" s="38">
+        <v>900151</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="N31" s="31"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
-    </row>
-    <row r="32" spans="1:28" ht="13.2">
-      <c r="A32" s="6">
-        <v>46084.76020355324</v>
-      </c>
-      <c r="B32" s="7">
-        <v>926814</v>
-      </c>
-      <c r="D32" s="8" t="s">
+      <c r="N46" s="30"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="10"/>
+      <c r="V46" s="10"/>
+    </row>
+    <row r="47" spans="1:25" ht="13.2">
+      <c r="A47" s="6">
+        <v>46086.336962430556</v>
+      </c>
+      <c r="B47" s="38">
+        <v>969081</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E47" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F47" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G47" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="N32" s="31"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
-      <c r="V32" s="8"/>
-    </row>
-    <row r="33" spans="2:28" ht="16.2">
-      <c r="B33" s="2">
-        <v>926826</v>
-      </c>
-      <c r="Z33" s="5" t="s">
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
+      <c r="V47" s="10"/>
+    </row>
+    <row r="48" spans="1:25" ht="13.2">
+      <c r="A48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48" s="41">
+        <v>224307</v>
+      </c>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G48" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="K48" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="L48" s="43"/>
+      <c r="M48" s="43"/>
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="43"/>
+      <c r="T48" s="43"/>
+      <c r="U48" s="43"/>
+      <c r="V48" s="43"/>
+      <c r="W48" s="25"/>
+    </row>
+    <row r="49" spans="1:30" ht="13.2">
+      <c r="A49" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B49" s="41">
+        <v>794418</v>
+      </c>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G49" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H49" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="K49" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="L49" s="43"/>
+      <c r="M49" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="N49" s="43"/>
+      <c r="O49" s="43"/>
+      <c r="P49" s="43"/>
+      <c r="Q49" s="43"/>
+      <c r="R49" s="43"/>
+      <c r="S49" s="43"/>
+      <c r="T49" s="43"/>
+      <c r="U49" s="43"/>
+      <c r="V49" s="43"/>
+      <c r="W49" s="26"/>
+    </row>
+    <row r="50" spans="1:30" ht="13.2">
+      <c r="A50" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B50" s="41">
+        <v>613493</v>
+      </c>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G50" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="J50" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="K50" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="L50" s="43"/>
+      <c r="M50" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="N50" s="43"/>
+      <c r="O50" s="43"/>
+      <c r="P50" s="43"/>
+      <c r="Q50" s="43"/>
+      <c r="R50" s="43"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="43"/>
+      <c r="U50" s="43"/>
+      <c r="V50" s="45"/>
+      <c r="W50" s="25"/>
+    </row>
+    <row r="51" spans="1:30" ht="13.2">
+      <c r="A51" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="B51" s="41">
+        <v>977328</v>
+      </c>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+      <c r="L51" s="43"/>
+      <c r="M51" s="43"/>
+      <c r="N51" s="43"/>
+      <c r="O51" s="43"/>
+      <c r="P51" s="43"/>
+      <c r="Q51" s="43"/>
+      <c r="R51" s="43"/>
+      <c r="S51" s="43"/>
+      <c r="T51" s="43"/>
+      <c r="U51" s="43"/>
+      <c r="V51" s="45"/>
+    </row>
+    <row r="52" spans="1:30" ht="13.2">
+      <c r="A52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B52" s="41">
+        <v>813675</v>
+      </c>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+      <c r="L52" s="43"/>
+      <c r="M52" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="N52" s="43"/>
+      <c r="O52" s="43"/>
+      <c r="P52" s="43"/>
+      <c r="Q52" s="43"/>
+      <c r="R52" s="43"/>
+      <c r="S52" s="43"/>
+      <c r="T52" s="43"/>
+      <c r="U52" s="43"/>
+      <c r="V52" s="43"/>
+    </row>
+    <row r="53" spans="1:30" ht="13.2">
+      <c r="A53" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B53" s="41">
+        <v>660872</v>
+      </c>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G53" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="L53" s="43"/>
+      <c r="M53" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="N53" s="43"/>
+      <c r="O53" s="43"/>
+      <c r="P53" s="43"/>
+      <c r="Q53" s="43"/>
+      <c r="R53" s="43"/>
+      <c r="S53" s="43"/>
+      <c r="T53" s="43"/>
+      <c r="U53" s="45"/>
+      <c r="V53" s="43"/>
+    </row>
+    <row r="54" spans="1:30" ht="16.2">
+      <c r="B54" s="2">
+        <v>121172</v>
+      </c>
+      <c r="U54" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z54" s="5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" ht="15">
-      <c r="B34" s="2">
-        <v>926927</v>
-      </c>
-    </row>
-    <row r="35" spans="2:28" ht="15">
-      <c r="B35" s="2">
-        <v>958658</v>
-      </c>
-      <c r="V35" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="2:28" ht="15">
-      <c r="B36" s="2">
-        <v>965552</v>
-      </c>
-      <c r="V36" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" ht="15">
-      <c r="B37" s="2">
-        <v>969081</v>
-      </c>
-      <c r="V37" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="2:28" ht="16.2">
-      <c r="B38" s="2">
+      <c r="AB54" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" ht="16.2">
+      <c r="A55" s="26"/>
+      <c r="B55" s="38">
+        <v>121172</v>
+      </c>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="51"/>
+      <c r="O55" s="26"/>
+      <c r="P55" s="26"/>
+      <c r="Q55" s="26"/>
+      <c r="R55" s="26"/>
+      <c r="S55" s="26"/>
+      <c r="T55" s="26"/>
+      <c r="U55" s="26"/>
+      <c r="V55" s="26"/>
+      <c r="AD55" s="35" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" ht="16.2">
+      <c r="A56" s="26"/>
+      <c r="B56" s="49">
+        <v>159297</v>
+      </c>
+      <c r="C56" s="50"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="51"/>
+      <c r="O56" s="26"/>
+      <c r="P56" s="26"/>
+      <c r="Q56" s="26"/>
+      <c r="R56" s="26"/>
+      <c r="S56" s="26"/>
+      <c r="T56" s="26"/>
+      <c r="U56" s="26"/>
+      <c r="V56" s="26"/>
+      <c r="AC56" s="28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" ht="16.2">
+      <c r="B57" s="2">
+        <v>224307</v>
+      </c>
+      <c r="S57" s="25"/>
+      <c r="Z57" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB57" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" ht="16.2">
+      <c r="B58" s="2">
         <v>271003</v>
       </c>
-      <c r="O38" s="11" t="s">
+      <c r="O58" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="Q38" s="11" t="s">
+      <c r="Q58" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="Z38" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB38" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" ht="16.2">
-      <c r="B39" s="2">
-        <v>777829</v>
-      </c>
-      <c r="T39" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="W39" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="X39" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z39" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB39" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="2:28" ht="15">
-      <c r="B40" s="2">
-        <v>438515</v>
-      </c>
-    </row>
-    <row r="41" spans="2:28" ht="16.2">
-      <c r="B41" s="2">
-        <v>420048</v>
-      </c>
-      <c r="Y41" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z41" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB41" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="2:28" ht="16.2">
-      <c r="B42" s="2">
-        <v>572964</v>
-      </c>
-      <c r="Y42" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z42" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB42" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" spans="2:28" ht="16.2">
-      <c r="B43" s="2">
-        <v>572990</v>
-      </c>
-      <c r="X43" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y43" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z43" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB43" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="44" spans="2:28" ht="16.2">
-      <c r="B44" s="2">
-        <v>667802</v>
-      </c>
-      <c r="Z44" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB44" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="2:28" ht="16.2">
-      <c r="B45" s="2">
-        <v>667725</v>
-      </c>
-      <c r="Z45" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB45" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="2:28" ht="15">
-      <c r="B46" s="2">
-        <v>813927</v>
-      </c>
-    </row>
-    <row r="47" spans="2:28" ht="16.2">
-      <c r="B47" s="2">
-        <v>926865</v>
-      </c>
-      <c r="Z47" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB47" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="2:28" ht="16.2">
-      <c r="B48" s="2">
-        <v>919959</v>
-      </c>
-      <c r="W48" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z48" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB48" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="49" spans="2:28" ht="16.2">
-      <c r="B49" s="2">
-        <v>956502</v>
-      </c>
-      <c r="Z49" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB49" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="50" spans="2:28" ht="15">
-      <c r="B50" s="2">
-        <v>964698</v>
-      </c>
-      <c r="V50" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="W50" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="2:28" ht="15">
-      <c r="B51" s="2">
-        <v>995225</v>
-      </c>
-      <c r="V51" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="2:28" ht="15">
-      <c r="B52" s="2">
-        <v>530877</v>
-      </c>
-    </row>
-    <row r="53" spans="2:28" ht="16.2">
-      <c r="B53" s="2">
-        <v>121172</v>
-      </c>
-      <c r="U53" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z53" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB53" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" spans="2:28" ht="15">
-      <c r="B54" s="2">
-        <v>441802</v>
-      </c>
-    </row>
-    <row r="55" spans="2:28" ht="15">
-      <c r="B55" s="2">
-        <v>667903</v>
-      </c>
-    </row>
-    <row r="56" spans="2:28" ht="15">
-      <c r="B56" s="2">
-        <v>926941</v>
-      </c>
-    </row>
-    <row r="57" spans="2:28" ht="15">
-      <c r="B57" s="2">
-        <v>926814</v>
-      </c>
-      <c r="S57" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="58" spans="2:28" ht="16.2">
-      <c r="B58" s="2">
-        <v>613493</v>
-      </c>
+      <c r="U58" s="26"/>
       <c r="Z58" s="5" t="s">
         <v>88</v>
       </c>
       <c r="AB58" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="59" spans="2:28" ht="16.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" ht="16.2">
       <c r="B59" s="2">
-        <v>224307</v>
+        <v>420048</v>
+      </c>
+      <c r="Y59" s="24" t="s">
+        <v>95</v>
       </c>
       <c r="Z59" s="5" t="s">
         <v>88</v>
       </c>
       <c r="AB59" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="2:28" ht="15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" ht="15">
       <c r="B60" s="2">
+        <v>438515</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" ht="15">
+      <c r="B61" s="2">
         <v>440471</v>
       </c>
     </row>
-    <row r="61" spans="2:28" ht="15">
-      <c r="B61" s="2">
+    <row r="62" spans="1:30" ht="15">
+      <c r="B62" s="2">
+        <v>441802</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" ht="15">
+      <c r="B63" s="2">
         <v>485918</v>
       </c>
     </row>
-    <row r="62" spans="2:28" ht="16.2">
-      <c r="B62" s="2">
+    <row r="64" spans="1:30" ht="15">
+      <c r="B64" s="2">
+        <v>530877</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29" ht="15">
+      <c r="B65" s="2">
+        <v>535474</v>
+      </c>
+    </row>
+    <row r="66" spans="1:29" ht="16.2">
+      <c r="B66" s="2">
+        <v>572964</v>
+      </c>
+      <c r="S66" s="26"/>
+      <c r="Y66" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z66" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB66" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" spans="1:29" ht="16.2">
+      <c r="B67" s="2">
+        <v>572990</v>
+      </c>
+      <c r="X67" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y67" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z67" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB67" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68" spans="1:29" ht="16.2">
+      <c r="B68" s="2">
+        <v>613493</v>
+      </c>
+      <c r="Z68" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB68" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" ht="16.2">
+      <c r="A69" s="26"/>
+      <c r="B69" s="49">
+        <v>613493</v>
+      </c>
+      <c r="C69" s="50"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="26"/>
+      <c r="N69" s="51"/>
+      <c r="O69" s="26"/>
+      <c r="P69" s="26"/>
+      <c r="Q69" s="26"/>
+      <c r="R69" s="26"/>
+      <c r="S69" s="26"/>
+      <c r="T69" s="26"/>
+      <c r="U69" s="26"/>
+      <c r="V69" s="26"/>
+      <c r="AC69" s="28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" ht="15">
+      <c r="B70" s="2">
+        <v>614230</v>
+      </c>
+      <c r="V70" s="26"/>
+    </row>
+    <row r="71" spans="1:29" ht="16.2">
+      <c r="B71" s="37">
         <v>660872</v>
       </c>
-      <c r="Z62" s="5" t="s">
+      <c r="T71" s="26"/>
+      <c r="W71" s="26"/>
+      <c r="X71" s="26"/>
+      <c r="Z71" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="63" spans="2:28" ht="15">
-      <c r="B63" s="2">
+    <row r="72" spans="1:29" ht="16.2">
+      <c r="B72" s="37">
+        <v>667725</v>
+      </c>
+      <c r="Y72" s="26"/>
+      <c r="Z72" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB72" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" ht="16.2">
+      <c r="B73" s="37">
+        <v>667802</v>
+      </c>
+      <c r="Z73" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB73" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" ht="15">
+      <c r="B74" s="37">
+        <v>667903</v>
+      </c>
+    </row>
+    <row r="75" spans="1:29" ht="16.2">
+      <c r="B75" s="37">
+        <v>777829</v>
+      </c>
+      <c r="T75" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="W75" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="X75" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z75" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB75" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" ht="15">
+      <c r="B76" s="37">
         <v>794418</v>
       </c>
-    </row>
-    <row r="64" spans="2:28" ht="15">
-      <c r="B64" s="2">
+      <c r="V76" s="26"/>
+    </row>
+    <row r="77" spans="1:29" ht="15">
+      <c r="B77" s="37">
         <v>813675</v>
       </c>
     </row>
-    <row r="65" spans="1:22" ht="15">
-      <c r="B65" s="2">
+    <row r="78" spans="1:29" ht="15">
+      <c r="B78" s="37">
+        <v>813927</v>
+      </c>
+      <c r="S78" s="26"/>
+    </row>
+    <row r="79" spans="1:29" ht="15">
+      <c r="B79" s="37">
         <v>900151</v>
       </c>
     </row>
-    <row r="66" spans="1:22" ht="15">
-      <c r="B66" s="2">
-        <v>977316</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" ht="15">
-      <c r="B67" s="2">
-        <v>977328</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" ht="15">
-      <c r="B68" s="2">
-        <v>957504</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" ht="15">
-      <c r="B69" s="2">
-        <v>614230</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" ht="15">
-      <c r="B70" s="2">
-        <v>535474</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" ht="13.2">
-      <c r="A71" s="6">
-        <v>46078.486714120372</v>
-      </c>
-      <c r="B71" s="12">
+    <row r="80" spans="1:29" ht="16.2">
+      <c r="A80" s="26"/>
+      <c r="B80" s="47">
+        <v>900151</v>
+      </c>
+      <c r="C80" s="50"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="51"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
+      <c r="R80" s="26"/>
+      <c r="S80" s="26"/>
+      <c r="T80" s="26"/>
+      <c r="U80" s="26"/>
+      <c r="V80" s="26"/>
+      <c r="AC80" s="28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:31" ht="16.2">
+      <c r="A81" s="26"/>
+      <c r="B81" s="47">
+        <v>919946</v>
+      </c>
+      <c r="C81" s="50"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="51"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="26"/>
+      <c r="Q81" s="26"/>
+      <c r="R81" s="26"/>
+      <c r="S81" s="26"/>
+      <c r="T81" s="26"/>
+      <c r="U81" s="26"/>
+      <c r="V81" s="26"/>
+      <c r="AC81" s="28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="82" spans="1:31" ht="16.2">
+      <c r="B82" s="37">
+        <v>919959</v>
+      </c>
+      <c r="W82" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z82" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB82" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="83" spans="1:31" ht="15">
+      <c r="B83" s="37">
+        <v>926814</v>
+      </c>
+      <c r="S83" s="24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:31" ht="16.2">
+      <c r="B84" s="37">
+        <v>926826</v>
+      </c>
+      <c r="W84" s="26"/>
+      <c r="Z84" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:31" ht="16.2">
+      <c r="B85" s="37">
         <v>926865</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H71" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K71" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="N71" s="31"/>
-      <c r="O71" s="8"/>
-      <c r="P71" s="8"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="8"/>
-      <c r="U71" s="8"/>
-      <c r="V71" s="8"/>
-    </row>
-    <row r="72" spans="1:22" ht="13.2">
-      <c r="A72" s="6">
-        <v>46078.484849120374</v>
-      </c>
-      <c r="B72" s="12">
+      <c r="Z85" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB85" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:31" ht="15.75" customHeight="1">
+      <c r="B86" s="37">
         <v>926927</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N72" s="31"/>
-      <c r="O72" s="8"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="8"/>
-      <c r="R72" s="8"/>
-      <c r="S72" s="8"/>
-      <c r="T72" s="8"/>
-      <c r="U72" s="8"/>
-      <c r="V72" s="8"/>
-    </row>
-    <row r="73" spans="1:22" ht="13.2">
-      <c r="A73" s="6">
-        <v>46079.449516863431</v>
-      </c>
-      <c r="B73" s="12">
+    </row>
+    <row r="87" spans="1:31" ht="15.75" customHeight="1">
+      <c r="B87" s="37">
         <v>926941</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="M73" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N73" s="31"/>
-      <c r="O73" s="8"/>
-      <c r="P73" s="8"/>
-      <c r="Q73" s="8"/>
-      <c r="R73" s="8"/>
-      <c r="S73" s="8"/>
-      <c r="T73" s="8"/>
-      <c r="U73" s="8"/>
-      <c r="V73" s="8"/>
-    </row>
-    <row r="74" spans="1:22" ht="13.2">
-      <c r="A74" s="6">
-        <v>46078.500472997686</v>
-      </c>
-      <c r="B74" s="12">
-        <v>926826</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M74" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="N74" s="31"/>
-      <c r="O74" s="8"/>
-      <c r="P74" s="8"/>
-      <c r="Q74" s="8"/>
-      <c r="R74" s="8"/>
-      <c r="S74" s="8"/>
-      <c r="T74" s="8"/>
-      <c r="U74" s="8"/>
-      <c r="V74" s="8"/>
-    </row>
-    <row r="75" spans="1:22" ht="13.2">
-      <c r="A75" s="6">
-        <v>46084.742802141205</v>
-      </c>
-      <c r="B75" s="12">
-        <v>965552</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="N75" s="31"/>
-      <c r="O75" s="8"/>
-      <c r="P75" s="8"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="8"/>
-      <c r="U75" s="8"/>
-      <c r="V75" s="8"/>
-    </row>
-    <row r="76" spans="1:22" ht="13.2">
-      <c r="A76" s="6">
-        <v>46084.742829363429</v>
-      </c>
-      <c r="B76" s="12">
-        <v>965552</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="N76" s="31"/>
-      <c r="O76" s="8"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="8"/>
-      <c r="U76" s="8"/>
-      <c r="V76" s="8"/>
-    </row>
-    <row r="77" spans="1:22" ht="13.2">
-      <c r="A77" s="6">
-        <v>46078.482949444442</v>
-      </c>
-      <c r="B77" s="12">
-        <v>956502</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N77" s="31"/>
-      <c r="O77" s="8"/>
-      <c r="P77" s="8"/>
-      <c r="Q77" s="8"/>
-      <c r="R77" s="8"/>
-      <c r="S77" s="8"/>
-      <c r="T77" s="8"/>
-      <c r="U77" s="8"/>
-      <c r="V77" s="8"/>
-    </row>
-    <row r="78" spans="1:22" ht="13.2">
-      <c r="A78" s="6">
-        <v>46078.651622349542</v>
-      </c>
-      <c r="B78" s="12">
-        <v>958658</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N78" s="31"/>
-      <c r="O78" s="8"/>
-      <c r="P78" s="8"/>
-      <c r="Q78" s="8"/>
-      <c r="R78" s="8"/>
-      <c r="S78" s="8"/>
-      <c r="T78" s="8"/>
-      <c r="U78" s="8"/>
-      <c r="V78" s="8"/>
-    </row>
-    <row r="79" spans="1:22" ht="13.2">
-      <c r="A79" s="6">
-        <v>46084.742841701387</v>
-      </c>
-      <c r="B79" s="12">
-        <v>965552</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="N79" s="31"/>
-      <c r="O79" s="8"/>
-      <c r="P79" s="8"/>
-      <c r="Q79" s="8"/>
-      <c r="R79" s="8"/>
-      <c r="S79" s="8"/>
-      <c r="T79" s="8"/>
-      <c r="U79" s="8"/>
-      <c r="V79" s="8"/>
-    </row>
-    <row r="80" spans="1:22" ht="13.2">
-      <c r="A80" s="6">
-        <v>46084.800993645833</v>
-      </c>
-      <c r="B80" s="12">
-        <v>977316</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
-      <c r="N80" s="31"/>
-      <c r="O80" s="8"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="8"/>
-      <c r="R80" s="8"/>
-      <c r="S80" s="8"/>
-      <c r="T80" s="8"/>
-      <c r="U80" s="8"/>
-      <c r="V80" s="8"/>
-    </row>
-    <row r="81" spans="1:31" ht="16.2">
-      <c r="A81" s="6">
-        <v>46080.641628287034</v>
-      </c>
-      <c r="B81" s="12">
-        <v>964698</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N81" s="31"/>
-      <c r="O81" s="8"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="8"/>
-      <c r="R81" s="8"/>
-      <c r="S81" s="8"/>
-      <c r="T81" s="8"/>
-      <c r="U81" s="8"/>
-      <c r="V81" s="8"/>
-      <c r="Z81" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB81" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="82" spans="1:31" ht="13.2">
-      <c r="A82" s="6">
-        <v>46078.534898900463</v>
-      </c>
-      <c r="B82" s="12">
-        <v>969081</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-      <c r="N82" s="31"/>
-      <c r="O82" s="8"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="8"/>
-      <c r="R82" s="8"/>
-      <c r="S82" s="8"/>
-      <c r="T82" s="8"/>
-      <c r="U82" s="8"/>
-      <c r="V82" s="8"/>
-    </row>
-    <row r="83" spans="1:31" ht="13.2">
-      <c r="A83" s="6">
-        <v>46086.336962430556</v>
-      </c>
-      <c r="B83" s="12">
-        <v>969081</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="31"/>
-      <c r="O83" s="8"/>
-      <c r="P83" s="8"/>
-      <c r="Q83" s="8"/>
-      <c r="R83" s="8"/>
-      <c r="S83" s="8"/>
-      <c r="T83" s="8"/>
-      <c r="U83" s="8"/>
-      <c r="V83" s="8"/>
-    </row>
-    <row r="84" spans="1:31" ht="13.2">
-      <c r="A84" s="6">
-        <v>46084.801018819446</v>
-      </c>
-      <c r="B84" s="12">
-        <v>977316</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H84" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-      <c r="N84" s="31"/>
-      <c r="O84" s="8"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
-      <c r="S84" s="8"/>
-      <c r="T84" s="8"/>
-      <c r="U84" s="8"/>
-      <c r="V84" s="8"/>
-    </row>
-    <row r="85" spans="1:31" ht="13.2">
-      <c r="A85" s="6">
-        <v>46079.435836782402</v>
-      </c>
-      <c r="B85" s="12">
-        <v>995225</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="31"/>
-      <c r="O85" s="8"/>
-      <c r="P85" s="8"/>
-      <c r="Q85" s="8"/>
-      <c r="R85" s="8"/>
-      <c r="S85" s="8"/>
-      <c r="T85" s="8"/>
-      <c r="U85" s="8"/>
-      <c r="V85" s="8"/>
-    </row>
-    <row r="86" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B86" s="12">
-        <v>926941</v>
-      </c>
-      <c r="AE86" s="36" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="87" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B87" s="12">
-        <v>964698</v>
-      </c>
-      <c r="AE87" s="36" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="88" spans="1:31" ht="15.75" customHeight="1">
       <c r="B88" s="12">
-        <v>121172</v>
-      </c>
-      <c r="AD88" s="36" t="s">
-        <v>174</v>
+        <v>926941</v>
+      </c>
+      <c r="AE88" s="35" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="89" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B89" s="29">
-        <v>919946</v>
-      </c>
-      <c r="C89" s="28"/>
-      <c r="AC89" s="28" t="s">
-        <v>171</v>
+      <c r="B89" s="37">
+        <v>956502</v>
+      </c>
+      <c r="Z89" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB89" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B90" s="29">
-        <v>159297</v>
-      </c>
-      <c r="C90" s="28"/>
-      <c r="AC90" s="28" t="s">
-        <v>171</v>
+      <c r="B90" s="37">
+        <v>957504</v>
       </c>
     </row>
     <row r="91" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B91" s="29">
-        <v>613493</v>
-      </c>
-      <c r="C91" s="28"/>
-      <c r="AC91" s="28" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="92" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B92" s="29">
-        <v>900151</v>
-      </c>
-      <c r="C92" s="28"/>
-      <c r="AC92" s="28" t="s">
-        <v>172</v>
+      <c r="B91" s="37">
+        <v>958658</v>
+      </c>
+      <c r="V91" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="W91" s="26"/>
+    </row>
+    <row r="92" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B92" s="37">
+        <v>964698</v>
+      </c>
+      <c r="V92" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="W92" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="93" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A93" s="40"/>
+      <c r="B93" s="42">
+        <v>964698</v>
+      </c>
+      <c r="C93" s="40"/>
+      <c r="D93" s="40"/>
+      <c r="E93" s="40"/>
+      <c r="F93" s="40"/>
+      <c r="G93" s="40"/>
+      <c r="H93" s="40"/>
+      <c r="I93" s="40"/>
+      <c r="J93" s="40"/>
+      <c r="K93" s="40"/>
+      <c r="L93" s="40"/>
+      <c r="M93" s="40"/>
+      <c r="N93" s="44"/>
+      <c r="O93" s="40"/>
+      <c r="P93" s="40"/>
+      <c r="Q93" s="40"/>
+      <c r="R93" s="40"/>
+      <c r="S93" s="40"/>
+      <c r="T93" s="40"/>
+      <c r="U93" s="40"/>
+      <c r="V93" s="40"/>
+      <c r="AE93" s="35" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="94" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A94" s="40"/>
+      <c r="B94" s="48">
+        <v>965552</v>
+      </c>
+      <c r="C94" s="40"/>
+      <c r="D94" s="40"/>
+      <c r="E94" s="40"/>
+      <c r="F94" s="40"/>
+      <c r="G94" s="40"/>
+      <c r="H94" s="40"/>
+      <c r="I94" s="40"/>
+      <c r="J94" s="40"/>
+      <c r="K94" s="40"/>
+      <c r="L94" s="40"/>
+      <c r="M94" s="40"/>
+      <c r="N94" s="44"/>
+      <c r="O94" s="40"/>
+      <c r="P94" s="40"/>
+      <c r="Q94" s="40"/>
+      <c r="R94" s="40"/>
+      <c r="S94" s="40"/>
+      <c r="T94" s="40"/>
+      <c r="U94" s="40"/>
+      <c r="V94" s="53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A95" s="40"/>
+      <c r="B95" s="48">
+        <v>969081</v>
+      </c>
+      <c r="C95" s="40"/>
+      <c r="D95" s="40"/>
+      <c r="E95" s="40"/>
+      <c r="F95" s="40"/>
+      <c r="G95" s="40"/>
+      <c r="H95" s="40"/>
+      <c r="I95" s="40"/>
+      <c r="J95" s="40"/>
+      <c r="K95" s="40"/>
+      <c r="L95" s="40"/>
+      <c r="M95" s="40"/>
+      <c r="N95" s="44"/>
+      <c r="O95" s="40"/>
+      <c r="P95" s="40"/>
+      <c r="Q95" s="40"/>
+      <c r="R95" s="40"/>
+      <c r="S95" s="40"/>
+      <c r="T95" s="40"/>
+      <c r="U95" s="40"/>
+      <c r="V95" s="53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A96" s="40"/>
+      <c r="B96" s="48">
+        <v>977316</v>
+      </c>
+      <c r="C96" s="40"/>
+      <c r="D96" s="40"/>
+      <c r="E96" s="40"/>
+      <c r="F96" s="40"/>
+      <c r="G96" s="40"/>
+      <c r="H96" s="40"/>
+      <c r="I96" s="40"/>
+      <c r="J96" s="40"/>
+      <c r="K96" s="40"/>
+      <c r="L96" s="40"/>
+      <c r="M96" s="40"/>
+      <c r="N96" s="44"/>
+      <c r="O96" s="40"/>
+      <c r="P96" s="40"/>
+      <c r="Q96" s="40"/>
+      <c r="R96" s="40"/>
+      <c r="S96" s="40"/>
+      <c r="T96" s="40"/>
+      <c r="U96" s="40"/>
+      <c r="V96" s="40"/>
+    </row>
+    <row r="97" spans="1:22" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A97" s="40"/>
+      <c r="B97" s="48">
+        <v>977328</v>
+      </c>
+      <c r="C97" s="40"/>
+      <c r="D97" s="40"/>
+      <c r="E97" s="40"/>
+      <c r="F97" s="40"/>
+      <c r="G97" s="40"/>
+      <c r="H97" s="40"/>
+      <c r="I97" s="40"/>
+      <c r="J97" s="40"/>
+      <c r="K97" s="40"/>
+      <c r="L97" s="40"/>
+      <c r="M97" s="40"/>
+      <c r="N97" s="44"/>
+      <c r="O97" s="40"/>
+      <c r="P97" s="40"/>
+      <c r="Q97" s="40"/>
+      <c r="R97" s="40"/>
+      <c r="S97" s="40"/>
+      <c r="T97" s="40"/>
+      <c r="U97" s="40"/>
+      <c r="V97" s="40"/>
+    </row>
+    <row r="98" spans="1:22" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A98" s="40"/>
+      <c r="B98" s="48">
+        <v>995225</v>
+      </c>
+      <c r="C98" s="40"/>
+      <c r="D98" s="40"/>
+      <c r="E98" s="40"/>
+      <c r="F98" s="40"/>
+      <c r="G98" s="40"/>
+      <c r="H98" s="40"/>
+      <c r="I98" s="40"/>
+      <c r="J98" s="40"/>
+      <c r="K98" s="40"/>
+      <c r="L98" s="40"/>
+      <c r="M98" s="40"/>
+      <c r="N98" s="44"/>
+      <c r="O98" s="40"/>
+      <c r="P98" s="40"/>
+      <c r="Q98" s="40"/>
+      <c r="R98" s="40"/>
+      <c r="S98" s="40"/>
+      <c r="T98" s="40"/>
+      <c r="U98" s="40"/>
+      <c r="V98" s="53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" ht="15.75" customHeight="1">
+      <c r="B99" s="56">
+        <v>957504</v>
+      </c>
+      <c r="E99" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F99" s="43" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB91">
-    <sortCondition ref="B2:B91"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AE99">
+    <sortCondition ref="A2:A99"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/問卷系統_月曆顯示.xlsx
+++ b/data/問卷系統_月曆顯示.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e7512d0a0cfb7bd/公司電腦/^N研測課長業務/^NClaude AI/訓練排程上網/資料庫自動化雲端更新/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2736A374-AB26-40EA-A5F9-A6029DB78C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EEF486C-306D-4BE3-8E80-5804D5D93405}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2736A374-AB26-40EA-A5F9-A6029DB78C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4016926-FECE-47BA-A0E9-6A47404BA64A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="184">
   <si>
     <t>代碼</t>
   </si>
@@ -677,6 +677,70 @@
     </r>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7/2(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <charset val="136"/>
+      </rPr>
+      <t>一天</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>一天</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -686,7 +750,7 @@
     <numFmt numFmtId="176" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="177" formatCode="m/d"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -802,6 +866,33 @@
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="7">
@@ -921,7 +1012,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1046,6 +1137,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1651,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AE90"/>
@@ -1784,7 +1876,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="2" spans="1:31" ht="13.2" customHeight="1">
       <c r="A2" s="35">
         <v>46079.470154050927</v>
       </c>
@@ -1841,7 +1933,7 @@
       </c>
       <c r="AB3" s="1"/>
     </row>
-    <row r="4" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="4" spans="1:31" ht="13.2" customHeight="1">
       <c r="B4" s="38">
         <v>121172</v>
       </c>
@@ -1849,7 +1941,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="5" spans="1:31" ht="13.2" customHeight="1">
       <c r="A5" s="35">
         <v>46078.495963310183</v>
       </c>
@@ -1892,7 +1984,7 @@
       <c r="U5" s="33"/>
       <c r="V5" s="33"/>
     </row>
-    <row r="6" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="6" spans="1:31" ht="13.2" customHeight="1">
       <c r="B6" s="44">
         <v>159297</v>
       </c>
@@ -1901,7 +1993,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="7" spans="1:31" ht="13.2" customHeight="1">
       <c r="A7" s="35" t="s">
         <v>99</v>
       </c>
@@ -1954,7 +2046,7 @@
       </c>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="9" spans="1:31" ht="13.2" customHeight="1">
       <c r="A9" s="35">
         <v>46078.667671388888</v>
       </c>
@@ -2051,7 +2143,7 @@
       </c>
       <c r="AB11" s="1"/>
     </row>
-    <row r="12" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="12" spans="1:31" ht="13.2" customHeight="1">
       <c r="A12" s="35">
         <v>46078.497951516198</v>
       </c>
@@ -2110,7 +2202,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="14" spans="1:31" ht="13.2" customHeight="1">
       <c r="A14" s="35">
         <v>46078.564764513889</v>
       </c>
@@ -2202,7 +2294,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="13.2" hidden="1" customHeight="1">
+    <row r="16" spans="1:31" ht="13.2" customHeight="1">
       <c r="A16" s="35">
         <v>46078.574391724527</v>
       </c>
@@ -2245,17 +2337,20 @@
       <c r="U16" s="33"/>
       <c r="V16" s="33"/>
     </row>
-    <row r="17" spans="1:28" ht="13.2" hidden="1" customHeight="1">
+    <row r="17" spans="1:28" ht="13.2" customHeight="1">
       <c r="B17" s="43">
         <v>438515</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="13.2" hidden="1" customHeight="1">
+    <row r="18" spans="1:28" ht="13.2" customHeight="1">
       <c r="A18" s="35">
         <v>46084.843648472219</v>
       </c>
       <c r="B18" s="38">
         <v>440471</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>182</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>57</v>
@@ -2287,12 +2382,15 @@
       <c r="U18" s="33"/>
       <c r="V18" s="33"/>
     </row>
-    <row r="19" spans="1:28" ht="13.2" hidden="1" customHeight="1">
+    <row r="19" spans="1:28" ht="13.2" customHeight="1">
       <c r="B19" s="43">
         <v>440471</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" ht="13.2" hidden="1" customHeight="1">
+      <c r="C19" s="53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" ht="13.2" customHeight="1">
       <c r="A20" s="35">
         <v>46078.568878067133</v>
       </c>
@@ -2337,12 +2435,12 @@
       <c r="U20" s="33"/>
       <c r="V20" s="33"/>
     </row>
-    <row r="21" spans="1:28" ht="13.2" hidden="1" customHeight="1">
+    <row r="21" spans="1:28" ht="13.2" customHeight="1">
       <c r="B21" s="43">
         <v>441802</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="13.2" hidden="1" customHeight="1">
+    <row r="22" spans="1:28" ht="13.2" customHeight="1">
       <c r="A22" s="35">
         <v>46078.568784780087</v>
       </c>
@@ -2379,17 +2477,17 @@
       <c r="U22" s="33"/>
       <c r="V22" s="33"/>
     </row>
-    <row r="23" spans="1:28" ht="13.2" hidden="1" customHeight="1">
+    <row r="23" spans="1:28" ht="13.2" customHeight="1">
       <c r="B23" s="43">
         <v>485918</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="16.2" hidden="1" customHeight="1">
+    <row r="24" spans="1:28" ht="16.2" customHeight="1">
       <c r="B24" s="43">
         <v>530877</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="16.2" hidden="1" customHeight="1">
+    <row r="25" spans="1:28" ht="16.2" customHeight="1">
       <c r="A25" s="35">
         <v>46078.617964687503</v>
       </c>
@@ -2422,7 +2520,7 @@
       <c r="U25" s="33"/>
       <c r="V25" s="33"/>
     </row>
-    <row r="26" spans="1:28" ht="16.2" hidden="1" customHeight="1">
+    <row r="26" spans="1:28" ht="16.2" customHeight="1">
       <c r="B26" s="43">
         <v>535474</v>
       </c>
@@ -2552,7 +2650,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="16.2" hidden="1" customHeight="1">
+    <row r="31" spans="1:28" ht="16.2" customHeight="1">
       <c r="A31" s="35" t="s">
         <v>101</v>
       </c>
@@ -2608,7 +2706,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="33" spans="1:29" ht="13.2" customHeight="1">
       <c r="B33" s="30">
         <v>613493</v>
       </c>
@@ -2618,7 +2716,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="34" spans="1:29" ht="13.2" customHeight="1">
       <c r="A34" s="35">
         <v>46084.829316446761</v>
       </c>
@@ -2651,7 +2749,7 @@
       <c r="X34" s="41"/>
       <c r="Y34" s="41"/>
     </row>
-    <row r="35" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="35" spans="1:29" ht="13.2" customHeight="1">
       <c r="A35" s="35">
         <v>46084.829352060187</v>
       </c>
@@ -2682,14 +2780,14 @@
       <c r="U35" s="33"/>
       <c r="V35" s="22"/>
     </row>
-    <row r="36" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="36" spans="1:29" ht="13.2" customHeight="1">
       <c r="B36" s="2">
         <v>614230</v>
       </c>
       <c r="O36" s="14"/>
       <c r="Q36" s="14"/>
     </row>
-    <row r="37" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="37" spans="1:29" ht="13.2" customHeight="1">
       <c r="A37" s="35" t="s">
         <v>104</v>
       </c>
@@ -2731,7 +2829,7 @@
       <c r="W37" s="14"/>
       <c r="X37" s="14"/>
     </row>
-    <row r="38" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="38" spans="1:29" ht="13.2" customHeight="1">
       <c r="B38" s="2">
         <v>660872</v>
       </c>
@@ -2739,7 +2837,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="39" spans="1:29" ht="13.2" customHeight="1">
       <c r="A39" s="35">
         <v>46078.520614456022</v>
       </c>
@@ -2814,7 +2912,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="42" spans="1:29" ht="13.2" customHeight="1">
       <c r="A42" s="35">
         <v>46078.48830921296</v>
       </c>
@@ -2906,7 +3004,7 @@
       </c>
       <c r="AB43" s="1"/>
     </row>
-    <row r="44" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="44" spans="1:29" ht="13.2" customHeight="1">
       <c r="A44" s="35">
         <v>46078.578018553242</v>
       </c>
@@ -2943,12 +3041,12 @@
       <c r="U44" s="33"/>
       <c r="V44" s="33"/>
     </row>
-    <row r="45" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="45" spans="1:29" ht="13.2" customHeight="1">
       <c r="B45" s="2">
         <v>667903</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="46" spans="1:29" ht="13.2" customHeight="1">
       <c r="A46" s="35">
         <v>46078.490101053241</v>
       </c>
@@ -3014,7 +3112,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="48" spans="1:29" ht="13.2" customHeight="1">
       <c r="A48" s="35" t="s">
         <v>100</v>
       </c>
@@ -3058,7 +3156,7 @@
       <c r="U48" s="25"/>
       <c r="V48" s="27"/>
     </row>
-    <row r="49" spans="1:29" ht="13.2" hidden="1" customHeight="1">
+    <row r="49" spans="1:29" ht="13.2" customHeight="1">
       <c r="B49" s="2">
         <v>794418</v>
       </c>
@@ -3075,7 +3173,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="16.2" hidden="1" customHeight="1">
+    <row r="51" spans="1:29" ht="16.2" customHeight="1">
       <c r="A51" s="35" t="s">
         <v>103</v>
       </c>
@@ -3111,7 +3209,7 @@
       <c r="U51" s="25"/>
       <c r="V51" s="25"/>
     </row>
-    <row r="52" spans="1:29" ht="16.2" hidden="1" customHeight="1">
+    <row r="52" spans="1:29" ht="16.2" customHeight="1">
       <c r="B52" s="2">
         <v>813675</v>
       </c>
@@ -3130,7 +3228,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="16.2" hidden="1" customHeight="1">
+    <row r="54" spans="1:29" ht="16.2" customHeight="1">
       <c r="A54" s="35">
         <v>46078.500563287038</v>
       </c>
@@ -3175,12 +3273,12 @@
       <c r="U54" s="33"/>
       <c r="V54" s="33"/>
     </row>
-    <row r="55" spans="1:29" ht="16.2" hidden="1" customHeight="1">
+    <row r="55" spans="1:29" ht="16.2" customHeight="1">
       <c r="B55" s="2">
         <v>813927</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="16.2" hidden="1" customHeight="1">
+    <row r="56" spans="1:29" ht="16.2" customHeight="1">
       <c r="A56" s="35">
         <v>46085.448310879627</v>
       </c>
@@ -3217,12 +3315,12 @@
       <c r="U56" s="33"/>
       <c r="V56" s="33"/>
     </row>
-    <row r="57" spans="1:29" ht="15" hidden="1" customHeight="1">
+    <row r="57" spans="1:29" ht="15" customHeight="1">
       <c r="B57" s="2">
         <v>900151</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="15" hidden="1" customHeight="1">
+    <row r="58" spans="1:29" ht="15" customHeight="1">
       <c r="B58" s="30">
         <v>900151</v>
       </c>
@@ -3231,7 +3329,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="15" hidden="1" customHeight="1">
+    <row r="59" spans="1:29" ht="15" customHeight="1">
       <c r="A59" s="35">
         <v>46084.736606354163</v>
       </c>
@@ -3274,7 +3372,7 @@
       <c r="U59" s="33"/>
       <c r="V59" s="33"/>
     </row>
-    <row r="60" spans="1:29" ht="15" hidden="1" customHeight="1">
+    <row r="60" spans="1:29" ht="15" customHeight="1">
       <c r="B60" s="30">
         <v>919946</v>
       </c>
@@ -3283,7 +3381,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="15" hidden="1" customHeight="1">
+    <row r="61" spans="1:29" ht="15" customHeight="1">
       <c r="A61" s="35">
         <v>46078.484767696762</v>
       </c>
@@ -3374,7 +3472,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="16.2" hidden="1" customHeight="1">
+    <row r="63" spans="1:29" ht="16.2" customHeight="1">
       <c r="A63" s="35">
         <v>46084.76020355324</v>
       </c>
@@ -3415,7 +3513,7 @@
       <c r="U63" s="33"/>
       <c r="V63" s="33"/>
     </row>
-    <row r="64" spans="1:29" ht="16.2" hidden="1" customHeight="1">
+    <row r="64" spans="1:29" ht="16.2" customHeight="1">
       <c r="B64" s="2">
         <v>926814</v>
       </c>
@@ -3423,7 +3521,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="16.2" hidden="1" customHeight="1">
+    <row r="65" spans="1:31" ht="16.2" customHeight="1">
       <c r="A65" s="35">
         <v>46078.500472997694</v>
       </c>
@@ -3464,7 +3562,7 @@
       <c r="U65" s="33"/>
       <c r="V65" s="33"/>
     </row>
-    <row r="66" spans="1:31" ht="15" hidden="1" customHeight="1">
+    <row r="66" spans="1:31" ht="15" customHeight="1">
       <c r="B66" s="2">
         <v>926826</v>
       </c>
@@ -3472,7 +3570,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="1:31" s="51" customFormat="1" ht="16.2" hidden="1" customHeight="1">
+    <row r="67" spans="1:31" s="51" customFormat="1" ht="16.2" customHeight="1">
       <c r="A67" s="49">
         <v>46078.486714120372</v>
       </c>
@@ -3564,7 +3662,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="16.2" hidden="1" customHeight="1">
+    <row r="69" spans="1:31" ht="16.2" customHeight="1">
       <c r="A69" s="35">
         <v>46079.449516863417</v>
       </c>
@@ -3606,12 +3704,12 @@
       <c r="V69" s="39"/>
       <c r="Y69" s="41"/>
     </row>
-    <row r="70" spans="1:31" ht="15" hidden="1" customHeight="1">
+    <row r="70" spans="1:31" ht="15" customHeight="1">
       <c r="B70" s="20">
         <v>926941</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="16.2" hidden="1" customHeight="1">
+    <row r="71" spans="1:31" ht="16.2" customHeight="1">
       <c r="B71" s="28">
         <v>926941</v>
       </c>
@@ -3619,7 +3717,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="15" hidden="1" customHeight="1">
+    <row r="72" spans="1:31" ht="15" customHeight="1">
       <c r="A72" s="35">
         <v>46078.482949444442</v>
       </c>
@@ -3708,12 +3806,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="15" hidden="1" customHeight="1">
+    <row r="74" spans="1:31" ht="15" customHeight="1">
       <c r="B74" s="20">
         <v>957504</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="15" hidden="1" customHeight="1">
+    <row r="75" spans="1:31" ht="15" customHeight="1">
       <c r="B75" s="43">
         <v>957504</v>
       </c>
@@ -3724,7 +3822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="16.2" hidden="1" customHeight="1">
+    <row r="76" spans="1:31" ht="16.2" customHeight="1">
       <c r="A76" s="35">
         <v>46078.651622349527</v>
       </c>
@@ -3764,7 +3862,7 @@
       <c r="V76" s="33"/>
       <c r="Y76" s="41"/>
     </row>
-    <row r="77" spans="1:31" ht="16.2" hidden="1" customHeight="1">
+    <row r="77" spans="1:31" ht="16.2" customHeight="1">
       <c r="B77" s="20">
         <v>958658</v>
       </c>
@@ -3789,7 +3887,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="15" hidden="1" customHeight="1">
+    <row r="79" spans="1:31" ht="15" customHeight="1">
       <c r="B79" s="20">
         <v>964698</v>
       </c>
@@ -3800,7 +3898,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="16.2" hidden="1" customHeight="1">
+    <row r="80" spans="1:31" ht="16.2" customHeight="1">
       <c r="A80" s="41"/>
       <c r="B80" s="38">
         <v>964698</v>
@@ -3829,7 +3927,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="15.75" hidden="1" customHeight="1">
+    <row r="81" spans="1:25" ht="15.75" customHeight="1">
       <c r="A81" s="35">
         <v>46084.742841701387</v>
       </c>
@@ -3866,7 +3964,7 @@
       <c r="U81" s="33"/>
       <c r="V81" s="33"/>
     </row>
-    <row r="82" spans="1:25" ht="15.75" hidden="1" customHeight="1">
+    <row r="82" spans="1:25" ht="15.75" customHeight="1">
       <c r="A82" s="41"/>
       <c r="B82" s="43">
         <v>965552</v>
@@ -3894,7 +3992,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="15.75" hidden="1" customHeight="1">
+    <row r="83" spans="1:25" ht="15.75" customHeight="1">
       <c r="A83" s="35">
         <v>46086.336962430563</v>
       </c>
@@ -3930,7 +4028,7 @@
       <c r="V83" s="39"/>
       <c r="W83" s="41"/>
     </row>
-    <row r="84" spans="1:25" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="84" spans="1:25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A84" s="41"/>
       <c r="B84" s="43">
         <v>969081</v>
@@ -3958,7 +4056,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="85" spans="1:25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A85" s="42">
         <v>46084.801018819453</v>
       </c>
@@ -3997,7 +4095,7 @@
       <c r="V85" s="47"/>
       <c r="Y85" s="41"/>
     </row>
-    <row r="86" spans="1:25" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="86" spans="1:25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A86" s="26"/>
       <c r="B86" s="29">
         <v>977316</v>
@@ -4023,7 +4121,7 @@
       <c r="U86" s="26"/>
       <c r="V86" s="26"/>
     </row>
-    <row r="87" spans="1:25" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="87" spans="1:25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A87" s="42" t="s">
         <v>102</v>
       </c>
@@ -4059,7 +4157,7 @@
       <c r="U87" s="46"/>
       <c r="V87" s="46"/>
     </row>
-    <row r="88" spans="1:25" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="88" spans="1:25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A88" s="26"/>
       <c r="B88" s="29">
         <v>977328</v>
@@ -4085,7 +4183,7 @@
       <c r="U88" s="26"/>
       <c r="V88" s="26"/>
     </row>
-    <row r="89" spans="1:25" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="89" spans="1:25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A89" s="42">
         <v>46079.43583678241</v>
       </c>
@@ -4119,7 +4217,7 @@
       <c r="U89" s="47"/>
       <c r="V89" s="47"/>
     </row>
-    <row r="90" spans="1:25" ht="15.75" hidden="1" customHeight="1">
+    <row r="90" spans="1:25" ht="15.75" customHeight="1">
       <c r="A90" s="41"/>
       <c r="B90" s="34">
         <v>995225</v>
@@ -4148,13 +4246,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE90" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="27">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AE90" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AE78">
     <sortCondition ref="AB2:AB90"/>
   </sortState>
@@ -11085,6 +11177,6 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>